--- a/filer/20342781_albatros.xlsx
+++ b/filer/20342781_albatros.xlsx
@@ -648,7 +648,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/20342781_albatros.xlsx
+++ b/filer/20342781_albatros.xlsx
@@ -10,8 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_20342781" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_20342781" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_20342781" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_20342781" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -202,11 +203,11 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -628,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -662,7 +663,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -677,35 +678,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1531,81 +1532,81 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>Immaterielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B23" s="11">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>Udviklingsprojekter</t>
+        </is>
+      </c>
+      <c r="B23" s="8">
         <f>'balance_raw_20342781'!$B$2</f>
         <v/>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="8">
         <f>'balance_raw_20342781'!$C$2</f>
         <v/>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="8">
         <f>'balance_raw_20342781'!$D$2</f>
         <v/>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="8">
         <f>'balance_raw_20342781'!$E$2</f>
         <v/>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="8">
         <f>'balance_raw_20342781'!$F$2</f>
         <v/>
       </c>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" s="12">
+      <c r="H23" s="9">
         <f>IFERROR(B23/$B$23*100,"")</f>
         <v/>
       </c>
-      <c r="I23" s="12">
+      <c r="I23" s="9">
         <f>IFERROR(C23/$B$23*100,"")</f>
         <v/>
       </c>
-      <c r="J23" s="12">
+      <c r="J23" s="9">
         <f>IFERROR(D23/$B$23*100,"")</f>
         <v/>
       </c>
-      <c r="K23" s="12">
+      <c r="K23" s="9">
         <f>IFERROR(E23/$B$23*100,"")</f>
         <v/>
       </c>
-      <c r="L23" s="12">
+      <c r="L23" s="9">
         <f>IFERROR(F23/$B$23*100,"")</f>
         <v/>
       </c>
@@ -1613,7 +1614,7 @@
     <row r="24" ht="16" customHeight="1">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Grunde og bygninger</t>
+          <t>Patenter, varemærker mv.</t>
         </is>
       </c>
       <c r="B24" s="5">
@@ -1661,7 +1662,7 @@
     <row r="25" ht="16" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Produktionsanlæg og maskiner</t>
+          <t>Goodwill</t>
         </is>
       </c>
       <c r="B25" s="8">
@@ -1707,49 +1708,49 @@
       </c>
     </row>
     <row r="26" ht="16" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Driftsmateriel og inventar</t>
-        </is>
-      </c>
-      <c r="B26" s="5">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Immaterielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B26" s="11">
         <f>'balance_raw_20342781'!$B$5</f>
         <v/>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="11">
         <f>'balance_raw_20342781'!$C$5</f>
         <v/>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="11">
         <f>'balance_raw_20342781'!$D$5</f>
         <v/>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="11">
         <f>'balance_raw_20342781'!$E$5</f>
         <v/>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="11">
         <f>'balance_raw_20342781'!$F$5</f>
         <v/>
       </c>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" s="6">
+      <c r="H26" s="12">
         <f>IFERROR(B26/$B$26*100,"")</f>
         <v/>
       </c>
-      <c r="I26" s="6">
+      <c r="I26" s="12">
         <f>IFERROR(C26/$B$26*100,"")</f>
         <v/>
       </c>
-      <c r="J26" s="6">
+      <c r="J26" s="12">
         <f>IFERROR(D26/$B$26*100,"")</f>
         <v/>
       </c>
-      <c r="K26" s="6">
+      <c r="K26" s="12">
         <f>IFERROR(E26/$B$26*100,"")</f>
         <v/>
       </c>
-      <c r="L26" s="6">
+      <c r="L26" s="12">
         <f>IFERROR(F26/$B$26*100,"")</f>
         <v/>
       </c>
@@ -1757,7 +1758,7 @@
     <row r="27" ht="16" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Indretning af lejede lokaler</t>
+          <t>Grunde og bygninger</t>
         </is>
       </c>
       <c r="B27" s="8">
@@ -1805,7 +1806,7 @@
     <row r="28" ht="16" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Forudbetaling og anlægsaktiver under opførelse</t>
+          <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
       <c r="B28" s="5">
@@ -1851,49 +1852,49 @@
       </c>
     </row>
     <row r="29" ht="16" customHeight="1">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t>Materielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B29" s="11">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Driftsmateriel og inventar</t>
+        </is>
+      </c>
+      <c r="B29" s="8">
         <f>'balance_raw_20342781'!$B$8</f>
         <v/>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="8">
         <f>'balance_raw_20342781'!$C$8</f>
         <v/>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="8">
         <f>'balance_raw_20342781'!$D$8</f>
         <v/>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="8">
         <f>'balance_raw_20342781'!$E$8</f>
         <v/>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="8">
         <f>'balance_raw_20342781'!$F$8</f>
         <v/>
       </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" s="12">
+      <c r="H29" s="9">
         <f>IFERROR(B29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="I29" s="12">
+      <c r="I29" s="9">
         <f>IFERROR(C29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="J29" s="12">
+      <c r="J29" s="9">
         <f>IFERROR(D29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="K29" s="12">
+      <c r="K29" s="9">
         <f>IFERROR(E29/$B$29*100,"")</f>
         <v/>
       </c>
-      <c r="L29" s="12">
+      <c r="L29" s="9">
         <f>IFERROR(F29/$B$29*100,"")</f>
         <v/>
       </c>
@@ -1901,7 +1902,7 @@
     <row r="30" ht="16" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Kapitalandele, dattervirksomheder</t>
+          <t>Indretning af lejede lokaler</t>
         </is>
       </c>
       <c r="B30" s="5">
@@ -1949,7 +1950,7 @@
     <row r="31" ht="16" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Deposita</t>
+          <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
       <c r="B31" s="8">
@@ -1997,7 +1998,7 @@
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t>Finansielle anlægsaktiver</t>
+          <t>Materielle anlægsaktiver</t>
         </is>
       </c>
       <c r="B32" s="11">
@@ -2043,49 +2044,49 @@
       </c>
     </row>
     <row r="33" ht="16" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B33" s="11">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
+          <t>Kapitalandele, dattervirksomheder</t>
+        </is>
+      </c>
+      <c r="B33" s="8">
         <f>'balance_raw_20342781'!$B$12</f>
         <v/>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="8">
         <f>'balance_raw_20342781'!$C$12</f>
         <v/>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="8">
         <f>'balance_raw_20342781'!$D$12</f>
         <v/>
       </c>
-      <c r="E33" s="11">
+      <c r="E33" s="8">
         <f>'balance_raw_20342781'!$E$12</f>
         <v/>
       </c>
-      <c r="F33" s="11">
+      <c r="F33" s="8">
         <f>'balance_raw_20342781'!$F$12</f>
         <v/>
       </c>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" s="12">
+      <c r="H33" s="9">
         <f>IFERROR(B33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="I33" s="12">
+      <c r="I33" s="9">
         <f>IFERROR(C33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="J33" s="12">
+      <c r="J33" s="9">
         <f>IFERROR(D33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="K33" s="12">
+      <c r="K33" s="9">
         <f>IFERROR(E33/$B$33*100,"")</f>
         <v/>
       </c>
-      <c r="L33" s="12">
+      <c r="L33" s="9">
         <f>IFERROR(F33/$B$33*100,"")</f>
         <v/>
       </c>
@@ -2093,7 +2094,7 @@
     <row r="34" ht="16" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Råvarer og hjælpematerialer</t>
+          <t>Deposita</t>
         </is>
       </c>
       <c r="B34" s="5">
@@ -2139,145 +2140,145 @@
       </c>
     </row>
     <row r="35" ht="16" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>Varer under fremstilling</t>
-        </is>
-      </c>
-      <c r="B35" s="8">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>Finansielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B35" s="11">
         <f>'balance_raw_20342781'!$B$14</f>
         <v/>
       </c>
-      <c r="C35" s="8">
+      <c r="C35" s="11">
         <f>'balance_raw_20342781'!$C$14</f>
         <v/>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="11">
         <f>'balance_raw_20342781'!$D$14</f>
         <v/>
       </c>
-      <c r="E35" s="8">
+      <c r="E35" s="11">
         <f>'balance_raw_20342781'!$E$14</f>
         <v/>
       </c>
-      <c r="F35" s="8">
+      <c r="F35" s="11">
         <f>'balance_raw_20342781'!$F$14</f>
         <v/>
       </c>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" s="9">
+      <c r="H35" s="12">
         <f>IFERROR(B35/$B$35*100,"")</f>
         <v/>
       </c>
-      <c r="I35" s="9">
+      <c r="I35" s="12">
         <f>IFERROR(C35/$B$35*100,"")</f>
         <v/>
       </c>
-      <c r="J35" s="9">
+      <c r="J35" s="12">
         <f>IFERROR(D35/$B$35*100,"")</f>
         <v/>
       </c>
-      <c r="K35" s="9">
+      <c r="K35" s="12">
         <f>IFERROR(E35/$B$35*100,"")</f>
         <v/>
       </c>
-      <c r="L35" s="9">
+      <c r="L35" s="12">
         <f>IFERROR(F35/$B$35*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="36" ht="16" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>Færdigvarer og handelsvarer</t>
-        </is>
-      </c>
-      <c r="B36" s="5">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>Anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B36" s="11">
         <f>'balance_raw_20342781'!$B$15</f>
         <v/>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="11">
         <f>'balance_raw_20342781'!$C$15</f>
         <v/>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="11">
         <f>'balance_raw_20342781'!$D$15</f>
         <v/>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="11">
         <f>'balance_raw_20342781'!$E$15</f>
         <v/>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="11">
         <f>'balance_raw_20342781'!$F$15</f>
         <v/>
       </c>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" s="6">
+      <c r="H36" s="12">
         <f>IFERROR(B36/$B$36*100,"")</f>
         <v/>
       </c>
-      <c r="I36" s="6">
+      <c r="I36" s="12">
         <f>IFERROR(C36/$B$36*100,"")</f>
         <v/>
       </c>
-      <c r="J36" s="6">
+      <c r="J36" s="12">
         <f>IFERROR(D36/$B$36*100,"")</f>
         <v/>
       </c>
-      <c r="K36" s="6">
+      <c r="K36" s="12">
         <f>IFERROR(E36/$B$36*100,"")</f>
         <v/>
       </c>
-      <c r="L36" s="6">
+      <c r="L36" s="12">
         <f>IFERROR(F36/$B$36*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16" customHeight="1">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>Varebeholdninger</t>
-        </is>
-      </c>
-      <c r="B37" s="11">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>Råvarer og hjælpematerialer</t>
+        </is>
+      </c>
+      <c r="B37" s="8">
         <f>'balance_raw_20342781'!$B$16</f>
         <v/>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="8">
         <f>'balance_raw_20342781'!$C$16</f>
         <v/>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="8">
         <f>'balance_raw_20342781'!$D$16</f>
         <v/>
       </c>
-      <c r="E37" s="11">
+      <c r="E37" s="8">
         <f>'balance_raw_20342781'!$E$16</f>
         <v/>
       </c>
-      <c r="F37" s="11">
+      <c r="F37" s="8">
         <f>'balance_raw_20342781'!$F$16</f>
         <v/>
       </c>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" s="12">
+      <c r="H37" s="9">
         <f>IFERROR(B37/$B$37*100,"")</f>
         <v/>
       </c>
-      <c r="I37" s="12">
+      <c r="I37" s="9">
         <f>IFERROR(C37/$B$37*100,"")</f>
         <v/>
       </c>
-      <c r="J37" s="12">
+      <c r="J37" s="9">
         <f>IFERROR(D37/$B$37*100,"")</f>
         <v/>
       </c>
-      <c r="K37" s="12">
+      <c r="K37" s="9">
         <f>IFERROR(E37/$B$37*100,"")</f>
         <v/>
       </c>
-      <c r="L37" s="12">
+      <c r="L37" s="9">
         <f>IFERROR(F37/$B$37*100,"")</f>
         <v/>
       </c>
@@ -2285,7 +2286,7 @@
     <row r="38" ht="16" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Tilgodehavender fra salg og tjenesteydelser</t>
+          <t>Varer under fremstilling</t>
         </is>
       </c>
       <c r="B38" s="5">
@@ -2333,7 +2334,7 @@
     <row r="39" ht="16" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Tilgodehavender hos tilknyttede virksomheder</t>
+          <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
       <c r="B39" s="8">
@@ -2379,49 +2380,49 @@
       </c>
     </row>
     <row r="40" ht="16" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Andre tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B40" s="5">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>Varebeholdninger</t>
+        </is>
+      </c>
+      <c r="B40" s="11">
         <f>'balance_raw_20342781'!$B$19</f>
         <v/>
       </c>
-      <c r="C40" s="5">
+      <c r="C40" s="11">
         <f>'balance_raw_20342781'!$C$19</f>
         <v/>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="11">
         <f>'balance_raw_20342781'!$D$19</f>
         <v/>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="11">
         <f>'balance_raw_20342781'!$E$19</f>
         <v/>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="11">
         <f>'balance_raw_20342781'!$F$19</f>
         <v/>
       </c>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" s="6">
+      <c r="H40" s="12">
         <f>IFERROR(B40/$B$40*100,"")</f>
         <v/>
       </c>
-      <c r="I40" s="6">
+      <c r="I40" s="12">
         <f>IFERROR(C40/$B$40*100,"")</f>
         <v/>
       </c>
-      <c r="J40" s="6">
+      <c r="J40" s="12">
         <f>IFERROR(D40/$B$40*100,"")</f>
         <v/>
       </c>
-      <c r="K40" s="6">
+      <c r="K40" s="12">
         <f>IFERROR(E40/$B$40*100,"")</f>
         <v/>
       </c>
-      <c r="L40" s="6">
+      <c r="L40" s="12">
         <f>IFERROR(F40/$B$40*100,"")</f>
         <v/>
       </c>
@@ -2429,7 +2430,7 @@
     <row r="41" ht="16" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (aktiver)</t>
+          <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
       <c r="B41" s="8">
@@ -2477,7 +2478,7 @@
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Udskudt skatteaktiv</t>
+          <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B42" s="5">
@@ -2525,7 +2526,7 @@
     <row r="43" ht="16" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
+          <t>Andre tilgodehavender</t>
         </is>
       </c>
       <c r="B43" s="8">
@@ -2573,7 +2574,7 @@
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>Kortfristede skattetilgodehavender</t>
+          <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
       <c r="B44" s="5">
@@ -2619,49 +2620,49 @@
       </c>
     </row>
     <row r="45" ht="16" customHeight="1">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>Tilgodehavender</t>
-        </is>
-      </c>
-      <c r="B45" s="11">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>Udskudt skatteaktiv</t>
+        </is>
+      </c>
+      <c r="B45" s="8">
         <f>'balance_raw_20342781'!$B$24</f>
         <v/>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="8">
         <f>'balance_raw_20342781'!$C$24</f>
         <v/>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="8">
         <f>'balance_raw_20342781'!$D$24</f>
         <v/>
       </c>
-      <c r="E45" s="11">
+      <c r="E45" s="8">
         <f>'balance_raw_20342781'!$E$24</f>
         <v/>
       </c>
-      <c r="F45" s="11">
+      <c r="F45" s="8">
         <f>'balance_raw_20342781'!$F$24</f>
         <v/>
       </c>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" s="12">
+      <c r="H45" s="9">
         <f>IFERROR(B45/$B$45*100,"")</f>
         <v/>
       </c>
-      <c r="I45" s="12">
+      <c r="I45" s="9">
         <f>IFERROR(C45/$B$45*100,"")</f>
         <v/>
       </c>
-      <c r="J45" s="12">
+      <c r="J45" s="9">
         <f>IFERROR(D45/$B$45*100,"")</f>
         <v/>
       </c>
-      <c r="K45" s="12">
+      <c r="K45" s="9">
         <f>IFERROR(E45/$B$45*100,"")</f>
         <v/>
       </c>
-      <c r="L45" s="12">
+      <c r="L45" s="9">
         <f>IFERROR(F45/$B$45*100,"")</f>
         <v/>
       </c>
@@ -2669,7 +2670,7 @@
     <row r="46" ht="16" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>Værdipapirer</t>
+          <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B46" s="5">
@@ -2717,7 +2718,7 @@
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>Likvide beholdninger</t>
+          <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
       <c r="B47" s="8">
@@ -2765,7 +2766,7 @@
     <row r="48" ht="16" customHeight="1">
       <c r="A48" s="10" t="inlineStr">
         <is>
-          <t>Omsætningsaktiver</t>
+          <t>Tilgodehavender</t>
         </is>
       </c>
       <c r="B48" s="11">
@@ -2811,239 +2812,239 @@
       </c>
     </row>
     <row r="49" ht="16" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Værdipapirer</t>
+        </is>
+      </c>
+      <c r="B49" s="8">
+        <f>'balance_raw_20342781'!$B$28</f>
+        <v/>
+      </c>
+      <c r="C49" s="8">
+        <f>'balance_raw_20342781'!$C$28</f>
+        <v/>
+      </c>
+      <c r="D49" s="8">
+        <f>'balance_raw_20342781'!$D$28</f>
+        <v/>
+      </c>
+      <c r="E49" s="8">
+        <f>'balance_raw_20342781'!$E$28</f>
+        <v/>
+      </c>
+      <c r="F49" s="8">
+        <f>'balance_raw_20342781'!$F$28</f>
+        <v/>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" s="9">
+        <f>IFERROR(B49/$B$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="I49" s="9">
+        <f>IFERROR(C49/$B$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="J49" s="9">
+        <f>IFERROR(D49/$B$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="K49" s="9">
+        <f>IFERROR(E49/$B$49*100,"")</f>
+        <v/>
+      </c>
+      <c r="L49" s="9">
+        <f>IFERROR(F49/$B$49*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Likvide beholdninger</t>
+        </is>
+      </c>
+      <c r="B50" s="5">
+        <f>'balance_raw_20342781'!$B$29</f>
+        <v/>
+      </c>
+      <c r="C50" s="5">
+        <f>'balance_raw_20342781'!$C$29</f>
+        <v/>
+      </c>
+      <c r="D50" s="5">
+        <f>'balance_raw_20342781'!$D$29</f>
+        <v/>
+      </c>
+      <c r="E50" s="5">
+        <f>'balance_raw_20342781'!$E$29</f>
+        <v/>
+      </c>
+      <c r="F50" s="5">
+        <f>'balance_raw_20342781'!$F$29</f>
+        <v/>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" s="6">
+        <f>IFERROR(B50/$B$50*100,"")</f>
+        <v/>
+      </c>
+      <c r="I50" s="6">
+        <f>IFERROR(C50/$B$50*100,"")</f>
+        <v/>
+      </c>
+      <c r="J50" s="6">
+        <f>IFERROR(D50/$B$50*100,"")</f>
+        <v/>
+      </c>
+      <c r="K50" s="6">
+        <f>IFERROR(E50/$B$50*100,"")</f>
+        <v/>
+      </c>
+      <c r="L50" s="6">
+        <f>IFERROR(F50/$B$50*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t>Omsætningsaktiver</t>
+        </is>
+      </c>
+      <c r="B51" s="11">
+        <f>'balance_raw_20342781'!$B$30</f>
+        <v/>
+      </c>
+      <c r="C51" s="11">
+        <f>'balance_raw_20342781'!$C$30</f>
+        <v/>
+      </c>
+      <c r="D51" s="11">
+        <f>'balance_raw_20342781'!$D$30</f>
+        <v/>
+      </c>
+      <c r="E51" s="11">
+        <f>'balance_raw_20342781'!$E$30</f>
+        <v/>
+      </c>
+      <c r="F51" s="11">
+        <f>'balance_raw_20342781'!$F$30</f>
+        <v/>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" s="12">
+        <f>IFERROR(B51/$B$51*100,"")</f>
+        <v/>
+      </c>
+      <c r="I51" s="12">
+        <f>IFERROR(C51/$B$51*100,"")</f>
+        <v/>
+      </c>
+      <c r="J51" s="12">
+        <f>IFERROR(D51/$B$51*100,"")</f>
+        <v/>
+      </c>
+      <c r="K51" s="12">
+        <f>IFERROR(E51/$B$51*100,"")</f>
+        <v/>
+      </c>
+      <c r="L51" s="12">
+        <f>IFERROR(F51/$B$51*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B49" s="11">
-        <f>'balance_raw_20342781'!$B$28</f>
-        <v/>
-      </c>
-      <c r="C49" s="11">
-        <f>'balance_raw_20342781'!$C$28</f>
-        <v/>
-      </c>
-      <c r="D49" s="11">
-        <f>'balance_raw_20342781'!$D$28</f>
-        <v/>
-      </c>
-      <c r="E49" s="11">
-        <f>'balance_raw_20342781'!$E$28</f>
-        <v/>
-      </c>
-      <c r="F49" s="11">
-        <f>'balance_raw_20342781'!$F$28</f>
-        <v/>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" s="12">
-        <f>IFERROR(B49/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="I49" s="12">
-        <f>IFERROR(C49/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="J49" s="12">
-        <f>IFERROR(D49/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="K49" s="12">
-        <f>IFERROR(E49/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="L49" s="12">
-        <f>IFERROR(F49/$B$49*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="B52" s="11">
+        <f>'balance_raw_20342781'!$B$31</f>
+        <v/>
+      </c>
+      <c r="C52" s="11">
+        <f>'balance_raw_20342781'!$C$31</f>
+        <v/>
+      </c>
+      <c r="D52" s="11">
+        <f>'balance_raw_20342781'!$D$31</f>
+        <v/>
+      </c>
+      <c r="E52" s="11">
+        <f>'balance_raw_20342781'!$E$31</f>
+        <v/>
+      </c>
+      <c r="F52" s="11">
+        <f>'balance_raw_20342781'!$F$31</f>
+        <v/>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" s="12">
+        <f>IFERROR(B52/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="I52" s="12">
+        <f>IFERROR(C52/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="J52" s="12">
+        <f>IFERROR(D52/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="K52" s="12">
+        <f>IFERROR(E52/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="L52" s="12">
+        <f>IFERROR(F52/$B$52*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>PASSIVER t.kr.</t>
         </is>
       </c>
-      <c r="B51" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C51" s="3" t="n">
+      <c r="B54" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="D51" s="3" t="n">
+      <c r="C54" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="E51" s="3" t="n">
+      <c r="D54" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="F51" s="3" t="n">
+      <c r="E54" s="3" t="n">
         <v>2024</v>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="I51" s="3" t="n">
+      <c r="F54" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="J51" s="3" t="n">
+      <c r="I54" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="K51" s="3" t="n">
+      <c r="J54" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="L51" s="3" t="n">
+      <c r="K54" s="3" t="n">
         <v>2024</v>
       </c>
-    </row>
-    <row r="52" ht="16" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>Selskabskapital</t>
-        </is>
-      </c>
-      <c r="B52" s="5">
-        <f>'balance_raw_20342781'!$B$29</f>
-        <v/>
-      </c>
-      <c r="C52" s="5">
-        <f>'balance_raw_20342781'!$C$29</f>
-        <v/>
-      </c>
-      <c r="D52" s="5">
-        <f>'balance_raw_20342781'!$D$29</f>
-        <v/>
-      </c>
-      <c r="E52" s="5">
-        <f>'balance_raw_20342781'!$E$29</f>
-        <v/>
-      </c>
-      <c r="F52" s="5">
-        <f>'balance_raw_20342781'!$F$29</f>
-        <v/>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" s="6">
-        <f>IFERROR(B52/$B$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="I52" s="6">
-        <f>IFERROR(C52/$B$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="J52" s="6">
-        <f>IFERROR(D52/$B$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="K52" s="6">
-        <f>IFERROR(E52/$B$52*100,"")</f>
-        <v/>
-      </c>
-      <c r="L52" s="6">
-        <f>IFERROR(F52/$B$52*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="16" customHeight="1">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
-        </is>
-      </c>
-      <c r="B53" s="8">
-        <f>'balance_raw_20342781'!$B$30</f>
-        <v/>
-      </c>
-      <c r="C53" s="8">
-        <f>'balance_raw_20342781'!$C$30</f>
-        <v/>
-      </c>
-      <c r="D53" s="8">
-        <f>'balance_raw_20342781'!$D$30</f>
-        <v/>
-      </c>
-      <c r="E53" s="8">
-        <f>'balance_raw_20342781'!$E$30</f>
-        <v/>
-      </c>
-      <c r="F53" s="8">
-        <f>'balance_raw_20342781'!$F$30</f>
-        <v/>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" s="9">
-        <f>IFERROR(B53/$B$53*100,"")</f>
-        <v/>
-      </c>
-      <c r="I53" s="9">
-        <f>IFERROR(C53/$B$53*100,"")</f>
-        <v/>
-      </c>
-      <c r="J53" s="9">
-        <f>IFERROR(D53/$B$53*100,"")</f>
-        <v/>
-      </c>
-      <c r="K53" s="9">
-        <f>IFERROR(E53/$B$53*100,"")</f>
-        <v/>
-      </c>
-      <c r="L53" s="9">
-        <f>IFERROR(F53/$B$53*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="16" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>Reserve for udviklingsomkostninger</t>
-        </is>
-      </c>
-      <c r="B54" s="5">
-        <f>'balance_raw_20342781'!$B$31</f>
-        <v/>
-      </c>
-      <c r="C54" s="5">
-        <f>'balance_raw_20342781'!$C$31</f>
-        <v/>
-      </c>
-      <c r="D54" s="5">
-        <f>'balance_raw_20342781'!$D$31</f>
-        <v/>
-      </c>
-      <c r="E54" s="5">
-        <f>'balance_raw_20342781'!$E$31</f>
-        <v/>
-      </c>
-      <c r="F54" s="5">
-        <f>'balance_raw_20342781'!$F$31</f>
-        <v/>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" s="6">
-        <f>IFERROR(B54/$B$54*100,"")</f>
-        <v/>
-      </c>
-      <c r="I54" s="6">
-        <f>IFERROR(C54/$B$54*100,"")</f>
-        <v/>
-      </c>
-      <c r="J54" s="6">
-        <f>IFERROR(D54/$B$54*100,"")</f>
-        <v/>
-      </c>
-      <c r="K54" s="6">
-        <f>IFERROR(E54/$B$54*100,"")</f>
-        <v/>
-      </c>
-      <c r="L54" s="6">
-        <f>IFERROR(F54/$B$54*100,"")</f>
-        <v/>
+      <c r="L54" s="3" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="55" ht="16" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>Reserve for sikringstransaktioner</t>
+          <t>Selskabskapital</t>
         </is>
       </c>
       <c r="B55" s="8">
@@ -3091,7 +3092,7 @@
     <row r="56" ht="16" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>Andre reserver</t>
+          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
       <c r="B56" s="5">
@@ -3139,7 +3140,7 @@
     <row r="57" ht="16" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>Overført resultat</t>
+          <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
       <c r="B57" s="8">
@@ -3185,49 +3186,49 @@
       </c>
     </row>
     <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="10" t="inlineStr">
-        <is>
-          <t>Egenkapital i alt</t>
-        </is>
-      </c>
-      <c r="B58" s="11">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>Reserve for sikringstransaktioner</t>
+        </is>
+      </c>
+      <c r="B58" s="5">
         <f>'balance_raw_20342781'!$B$35</f>
         <v/>
       </c>
-      <c r="C58" s="11">
+      <c r="C58" s="5">
         <f>'balance_raw_20342781'!$C$35</f>
         <v/>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="5">
         <f>'balance_raw_20342781'!$D$35</f>
         <v/>
       </c>
-      <c r="E58" s="11">
+      <c r="E58" s="5">
         <f>'balance_raw_20342781'!$E$35</f>
         <v/>
       </c>
-      <c r="F58" s="11">
+      <c r="F58" s="5">
         <f>'balance_raw_20342781'!$F$35</f>
         <v/>
       </c>
       <c r="G58" t="inlineStr"/>
-      <c r="H58" s="12">
+      <c r="H58" s="6">
         <f>IFERROR(B58/$B$58*100,"")</f>
         <v/>
       </c>
-      <c r="I58" s="12">
+      <c r="I58" s="6">
         <f>IFERROR(C58/$B$58*100,"")</f>
         <v/>
       </c>
-      <c r="J58" s="12">
+      <c r="J58" s="6">
         <f>IFERROR(D58/$B$58*100,"")</f>
         <v/>
       </c>
-      <c r="K58" s="12">
+      <c r="K58" s="6">
         <f>IFERROR(E58/$B$58*100,"")</f>
         <v/>
       </c>
-      <c r="L58" s="12">
+      <c r="L58" s="6">
         <f>IFERROR(F58/$B$58*100,"")</f>
         <v/>
       </c>
@@ -3235,7 +3236,7 @@
     <row r="59" ht="16" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>Hensættelse til udskudt skat</t>
+          <t>Andre reserver</t>
         </is>
       </c>
       <c r="B59" s="8">
@@ -3281,97 +3282,97 @@
       </c>
     </row>
     <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>Hensatte forpligtelser</t>
-        </is>
-      </c>
-      <c r="B60" s="11">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>Overført resultat</t>
+        </is>
+      </c>
+      <c r="B60" s="5">
         <f>'balance_raw_20342781'!$B$37</f>
         <v/>
       </c>
-      <c r="C60" s="11">
+      <c r="C60" s="5">
         <f>'balance_raw_20342781'!$C$37</f>
         <v/>
       </c>
-      <c r="D60" s="11">
+      <c r="D60" s="5">
         <f>'balance_raw_20342781'!$D$37</f>
         <v/>
       </c>
-      <c r="E60" s="11">
+      <c r="E60" s="5">
         <f>'balance_raw_20342781'!$E$37</f>
         <v/>
       </c>
-      <c r="F60" s="11">
+      <c r="F60" s="5">
         <f>'balance_raw_20342781'!$F$37</f>
         <v/>
       </c>
       <c r="G60" t="inlineStr"/>
-      <c r="H60" s="12">
+      <c r="H60" s="6">
         <f>IFERROR(B60/$B$60*100,"")</f>
         <v/>
       </c>
-      <c r="I60" s="12">
+      <c r="I60" s="6">
         <f>IFERROR(C60/$B$60*100,"")</f>
         <v/>
       </c>
-      <c r="J60" s="12">
+      <c r="J60" s="6">
         <f>IFERROR(D60/$B$60*100,"")</f>
         <v/>
       </c>
-      <c r="K60" s="12">
+      <c r="K60" s="6">
         <f>IFERROR(E60/$B$60*100,"")</f>
         <v/>
       </c>
-      <c r="L60" s="12">
+      <c r="L60" s="6">
         <f>IFERROR(F60/$B$60*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="16" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
-        </is>
-      </c>
-      <c r="B61" s="8">
+      <c r="A61" s="10" t="inlineStr">
+        <is>
+          <t>Egenkapital i alt</t>
+        </is>
+      </c>
+      <c r="B61" s="11">
         <f>'balance_raw_20342781'!$B$38</f>
         <v/>
       </c>
-      <c r="C61" s="8">
+      <c r="C61" s="11">
         <f>'balance_raw_20342781'!$C$38</f>
         <v/>
       </c>
-      <c r="D61" s="8">
+      <c r="D61" s="11">
         <f>'balance_raw_20342781'!$D$38</f>
         <v/>
       </c>
-      <c r="E61" s="8">
+      <c r="E61" s="11">
         <f>'balance_raw_20342781'!$E$38</f>
         <v/>
       </c>
-      <c r="F61" s="8">
+      <c r="F61" s="11">
         <f>'balance_raw_20342781'!$F$38</f>
         <v/>
       </c>
       <c r="G61" t="inlineStr"/>
-      <c r="H61" s="9">
+      <c r="H61" s="12">
         <f>IFERROR(B61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="I61" s="9">
+      <c r="I61" s="12">
         <f>IFERROR(C61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="J61" s="9">
+      <c r="J61" s="12">
         <f>IFERROR(D61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="K61" s="9">
+      <c r="K61" s="12">
         <f>IFERROR(E61/$B$61*100,"")</f>
         <v/>
       </c>
-      <c r="L61" s="9">
+      <c r="L61" s="12">
         <f>IFERROR(F61/$B$61*100,"")</f>
         <v/>
       </c>
@@ -3379,7 +3380,7 @@
     <row r="62" ht="16" customHeight="1">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Langfristede lån</t>
+          <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
       <c r="B62" s="5">
@@ -3425,49 +3426,49 @@
       </c>
     </row>
     <row r="63" ht="16" customHeight="1">
-      <c r="A63" s="7" t="inlineStr">
-        <is>
-          <t>Leasingforpligtelser (langfristet)</t>
-        </is>
-      </c>
-      <c r="B63" s="8">
+      <c r="A63" s="10" t="inlineStr">
+        <is>
+          <t>Hensatte forpligtelser</t>
+        </is>
+      </c>
+      <c r="B63" s="11">
         <f>'balance_raw_20342781'!$B$40</f>
         <v/>
       </c>
-      <c r="C63" s="8">
+      <c r="C63" s="11">
         <f>'balance_raw_20342781'!$C$40</f>
         <v/>
       </c>
-      <c r="D63" s="8">
+      <c r="D63" s="11">
         <f>'balance_raw_20342781'!$D$40</f>
         <v/>
       </c>
-      <c r="E63" s="8">
+      <c r="E63" s="11">
         <f>'balance_raw_20342781'!$E$40</f>
         <v/>
       </c>
-      <c r="F63" s="8">
+      <c r="F63" s="11">
         <f>'balance_raw_20342781'!$F$40</f>
         <v/>
       </c>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" s="9">
+      <c r="H63" s="12">
         <f>IFERROR(B63/$B$63*100,"")</f>
         <v/>
       </c>
-      <c r="I63" s="9">
+      <c r="I63" s="12">
         <f>IFERROR(C63/$B$63*100,"")</f>
         <v/>
       </c>
-      <c r="J63" s="9">
+      <c r="J63" s="12">
         <f>IFERROR(D63/$B$63*100,"")</f>
         <v/>
       </c>
-      <c r="K63" s="9">
+      <c r="K63" s="12">
         <f>IFERROR(E63/$B$63*100,"")</f>
         <v/>
       </c>
-      <c r="L63" s="9">
+      <c r="L63" s="12">
         <f>IFERROR(F63/$B$63*100,"")</f>
         <v/>
       </c>
@@ -3475,7 +3476,7 @@
     <row r="64" ht="16" customHeight="1">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Anden gæld (langfristet)</t>
+          <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
       <c r="B64" s="5">
@@ -3521,49 +3522,49 @@
       </c>
     </row>
     <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="10" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B65" s="11">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>Langfristede lån</t>
+        </is>
+      </c>
+      <c r="B65" s="8">
         <f>'balance_raw_20342781'!$B$42</f>
         <v/>
       </c>
-      <c r="C65" s="11">
+      <c r="C65" s="8">
         <f>'balance_raw_20342781'!$C$42</f>
         <v/>
       </c>
-      <c r="D65" s="11">
+      <c r="D65" s="8">
         <f>'balance_raw_20342781'!$D$42</f>
         <v/>
       </c>
-      <c r="E65" s="11">
+      <c r="E65" s="8">
         <f>'balance_raw_20342781'!$E$42</f>
         <v/>
       </c>
-      <c r="F65" s="11">
+      <c r="F65" s="8">
         <f>'balance_raw_20342781'!$F$42</f>
         <v/>
       </c>
       <c r="G65" t="inlineStr"/>
-      <c r="H65" s="12">
+      <c r="H65" s="9">
         <f>IFERROR(B65/$B$65*100,"")</f>
         <v/>
       </c>
-      <c r="I65" s="12">
+      <c r="I65" s="9">
         <f>IFERROR(C65/$B$65*100,"")</f>
         <v/>
       </c>
-      <c r="J65" s="12">
+      <c r="J65" s="9">
         <f>IFERROR(D65/$B$65*100,"")</f>
         <v/>
       </c>
-      <c r="K65" s="12">
+      <c r="K65" s="9">
         <f>IFERROR(E65/$B$65*100,"")</f>
         <v/>
       </c>
-      <c r="L65" s="12">
+      <c r="L65" s="9">
         <f>IFERROR(F65/$B$65*100,"")</f>
         <v/>
       </c>
@@ -3571,7 +3572,7 @@
     <row r="66" ht="16" customHeight="1">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
+          <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
       <c r="B66" s="5">
@@ -3619,7 +3620,7 @@
     <row r="67" ht="16" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+          <t>Anden gæld (langfristet)</t>
         </is>
       </c>
       <c r="B67" s="8">
@@ -3665,49 +3666,49 @@
       </c>
     </row>
     <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="4" t="inlineStr">
-        <is>
-          <t>Kreditinstitutter</t>
-        </is>
-      </c>
-      <c r="B68" s="5">
+      <c r="A68" s="10" t="inlineStr">
+        <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B68" s="11">
         <f>'balance_raw_20342781'!$B$45</f>
         <v/>
       </c>
-      <c r="C68" s="5">
+      <c r="C68" s="11">
         <f>'balance_raw_20342781'!$C$45</f>
         <v/>
       </c>
-      <c r="D68" s="5">
+      <c r="D68" s="11">
         <f>'balance_raw_20342781'!$D$45</f>
         <v/>
       </c>
-      <c r="E68" s="5">
+      <c r="E68" s="11">
         <f>'balance_raw_20342781'!$E$45</f>
         <v/>
       </c>
-      <c r="F68" s="5">
+      <c r="F68" s="11">
         <f>'balance_raw_20342781'!$F$45</f>
         <v/>
       </c>
       <c r="G68" t="inlineStr"/>
-      <c r="H68" s="6">
+      <c r="H68" s="12">
         <f>IFERROR(B68/$B$68*100,"")</f>
         <v/>
       </c>
-      <c r="I68" s="6">
+      <c r="I68" s="12">
         <f>IFERROR(C68/$B$68*100,"")</f>
         <v/>
       </c>
-      <c r="J68" s="6">
+      <c r="J68" s="12">
         <f>IFERROR(D68/$B$68*100,"")</f>
         <v/>
       </c>
-      <c r="K68" s="6">
+      <c r="K68" s="12">
         <f>IFERROR(E68/$B$68*100,"")</f>
         <v/>
       </c>
-      <c r="L68" s="6">
+      <c r="L68" s="12">
         <f>IFERROR(F68/$B$68*100,"")</f>
         <v/>
       </c>
@@ -3715,7 +3716,7 @@
     <row r="69" ht="16" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Leasingforpligtelser (kortfristet)</t>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
       <c r="B69" s="8">
@@ -3763,7 +3764,7 @@
     <row r="70" ht="16" customHeight="1">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Leverandører af varer og tjenesteydelser</t>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
       <c r="B70" s="5">
@@ -3811,7 +3812,7 @@
     <row r="71" ht="16" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder</t>
+          <t>Kreditinstitutter</t>
         </is>
       </c>
       <c r="B71" s="8">
@@ -3859,7 +3860,7 @@
     <row r="72" ht="16" customHeight="1">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Gæld til selskabsdeltagere og ledelse</t>
+          <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
       <c r="B72" s="5">
@@ -3907,7 +3908,7 @@
     <row r="73" ht="16" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>Selskabsskat</t>
+          <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
       <c r="B73" s="8">
@@ -3955,7 +3956,7 @@
     <row r="74" ht="16" customHeight="1">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+          <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
       <c r="B74" s="5">
@@ -4003,7 +4004,7 @@
     <row r="75" ht="16" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>Anden gæld (kortfristet)</t>
+          <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
       <c r="B75" s="8">
@@ -4051,7 +4052,7 @@
     <row r="76" ht="16" customHeight="1">
       <c r="A76" s="4" t="inlineStr">
         <is>
-          <t>Periodeafgrænsningsposter (passiver)</t>
+          <t>Selskabsskat</t>
         </is>
       </c>
       <c r="B76" s="5">
@@ -4097,583 +4098,869 @@
       </c>
     </row>
     <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="10" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr">
+        <is>
+          <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
+        </is>
+      </c>
+      <c r="B77" s="8">
+        <f>'balance_raw_20342781'!$B$54</f>
+        <v/>
+      </c>
+      <c r="C77" s="8">
+        <f>'balance_raw_20342781'!$C$54</f>
+        <v/>
+      </c>
+      <c r="D77" s="8">
+        <f>'balance_raw_20342781'!$D$54</f>
+        <v/>
+      </c>
+      <c r="E77" s="8">
+        <f>'balance_raw_20342781'!$E$54</f>
+        <v/>
+      </c>
+      <c r="F77" s="8">
+        <f>'balance_raw_20342781'!$F$54</f>
+        <v/>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" s="9">
+        <f>IFERROR(B77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="I77" s="9">
+        <f>IFERROR(C77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="J77" s="9">
+        <f>IFERROR(D77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="K77" s="9">
+        <f>IFERROR(E77/$B$77*100,"")</f>
+        <v/>
+      </c>
+      <c r="L77" s="9">
+        <f>IFERROR(F77/$B$77*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>Anden gæld (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B78" s="5">
+        <f>'balance_raw_20342781'!$B$55</f>
+        <v/>
+      </c>
+      <c r="C78" s="5">
+        <f>'balance_raw_20342781'!$C$55</f>
+        <v/>
+      </c>
+      <c r="D78" s="5">
+        <f>'balance_raw_20342781'!$D$55</f>
+        <v/>
+      </c>
+      <c r="E78" s="5">
+        <f>'balance_raw_20342781'!$E$55</f>
+        <v/>
+      </c>
+      <c r="F78" s="5">
+        <f>'balance_raw_20342781'!$F$55</f>
+        <v/>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" s="6">
+        <f>IFERROR(B78/$B$78*100,"")</f>
+        <v/>
+      </c>
+      <c r="I78" s="6">
+        <f>IFERROR(C78/$B$78*100,"")</f>
+        <v/>
+      </c>
+      <c r="J78" s="6">
+        <f>IFERROR(D78/$B$78*100,"")</f>
+        <v/>
+      </c>
+      <c r="K78" s="6">
+        <f>IFERROR(E78/$B$78*100,"")</f>
+        <v/>
+      </c>
+      <c r="L78" s="6">
+        <f>IFERROR(F78/$B$78*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="7" t="inlineStr">
+        <is>
+          <t>Periodeafgrænsningsposter (passiver)</t>
+        </is>
+      </c>
+      <c r="B79" s="8">
+        <f>'balance_raw_20342781'!$B$56</f>
+        <v/>
+      </c>
+      <c r="C79" s="8">
+        <f>'balance_raw_20342781'!$C$56</f>
+        <v/>
+      </c>
+      <c r="D79" s="8">
+        <f>'balance_raw_20342781'!$D$56</f>
+        <v/>
+      </c>
+      <c r="E79" s="8">
+        <f>'balance_raw_20342781'!$E$56</f>
+        <v/>
+      </c>
+      <c r="F79" s="8">
+        <f>'balance_raw_20342781'!$F$56</f>
+        <v/>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" s="9">
+        <f>IFERROR(B79/$B$79*100,"")</f>
+        <v/>
+      </c>
+      <c r="I79" s="9">
+        <f>IFERROR(C79/$B$79*100,"")</f>
+        <v/>
+      </c>
+      <c r="J79" s="9">
+        <f>IFERROR(D79/$B$79*100,"")</f>
+        <v/>
+      </c>
+      <c r="K79" s="9">
+        <f>IFERROR(E79/$B$79*100,"")</f>
+        <v/>
+      </c>
+      <c r="L79" s="9">
+        <f>IFERROR(F79/$B$79*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="10" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B77" s="11">
-        <f>'balance_raw_20342781'!$B$54</f>
-        <v/>
-      </c>
-      <c r="C77" s="11">
-        <f>'balance_raw_20342781'!$C$54</f>
-        <v/>
-      </c>
-      <c r="D77" s="11">
-        <f>'balance_raw_20342781'!$D$54</f>
-        <v/>
-      </c>
-      <c r="E77" s="11">
-        <f>'balance_raw_20342781'!$E$54</f>
-        <v/>
-      </c>
-      <c r="F77" s="11">
-        <f>'balance_raw_20342781'!$F$54</f>
-        <v/>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" s="12">
-        <f>IFERROR(B77/$B$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="I77" s="12">
-        <f>IFERROR(C77/$B$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="J77" s="12">
-        <f>IFERROR(D77/$B$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="K77" s="12">
-        <f>IFERROR(E77/$B$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="L77" s="12">
-        <f>IFERROR(F77/$B$77*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="10" t="inlineStr">
+      <c r="B80" s="11">
+        <f>'balance_raw_20342781'!$B$57</f>
+        <v/>
+      </c>
+      <c r="C80" s="11">
+        <f>'balance_raw_20342781'!$C$57</f>
+        <v/>
+      </c>
+      <c r="D80" s="11">
+        <f>'balance_raw_20342781'!$D$57</f>
+        <v/>
+      </c>
+      <c r="E80" s="11">
+        <f>'balance_raw_20342781'!$E$57</f>
+        <v/>
+      </c>
+      <c r="F80" s="11">
+        <f>'balance_raw_20342781'!$F$57</f>
+        <v/>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" s="12">
+        <f>IFERROR(B80/$B$80*100,"")</f>
+        <v/>
+      </c>
+      <c r="I80" s="12">
+        <f>IFERROR(C80/$B$80*100,"")</f>
+        <v/>
+      </c>
+      <c r="J80" s="12">
+        <f>IFERROR(D80/$B$80*100,"")</f>
+        <v/>
+      </c>
+      <c r="K80" s="12">
+        <f>IFERROR(E80/$B$80*100,"")</f>
+        <v/>
+      </c>
+      <c r="L80" s="12">
+        <f>IFERROR(F80/$B$80*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="10" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B78" s="11">
-        <f>'balance_raw_20342781'!$B$55</f>
-        <v/>
-      </c>
-      <c r="C78" s="11">
-        <f>'balance_raw_20342781'!$C$55</f>
-        <v/>
-      </c>
-      <c r="D78" s="11">
-        <f>'balance_raw_20342781'!$D$55</f>
-        <v/>
-      </c>
-      <c r="E78" s="11">
-        <f>'balance_raw_20342781'!$E$55</f>
-        <v/>
-      </c>
-      <c r="F78" s="11">
-        <f>'balance_raw_20342781'!$F$55</f>
-        <v/>
-      </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" s="12">
-        <f>IFERROR(B78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="I78" s="12">
-        <f>IFERROR(C78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="J78" s="12">
-        <f>IFERROR(D78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="K78" s="12">
-        <f>IFERROR(E78/$B$78*100,"")</f>
-        <v/>
-      </c>
-      <c r="L78" s="12">
-        <f>IFERROR(F78/$B$78*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="10" t="inlineStr">
+      <c r="B81" s="11">
+        <f>'balance_raw_20342781'!$B$58</f>
+        <v/>
+      </c>
+      <c r="C81" s="11">
+        <f>'balance_raw_20342781'!$C$58</f>
+        <v/>
+      </c>
+      <c r="D81" s="11">
+        <f>'balance_raw_20342781'!$D$58</f>
+        <v/>
+      </c>
+      <c r="E81" s="11">
+        <f>'balance_raw_20342781'!$E$58</f>
+        <v/>
+      </c>
+      <c r="F81" s="11">
+        <f>'balance_raw_20342781'!$F$58</f>
+        <v/>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" s="12">
+        <f>IFERROR(B81/$B$81*100,"")</f>
+        <v/>
+      </c>
+      <c r="I81" s="12">
+        <f>IFERROR(C81/$B$81*100,"")</f>
+        <v/>
+      </c>
+      <c r="J81" s="12">
+        <f>IFERROR(D81/$B$81*100,"")</f>
+        <v/>
+      </c>
+      <c r="K81" s="12">
+        <f>IFERROR(E81/$B$81*100,"")</f>
+        <v/>
+      </c>
+      <c r="L81" s="12">
+        <f>IFERROR(F81/$B$81*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="10" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B79" s="11">
-        <f>'balance_raw_20342781'!$B$56</f>
-        <v/>
-      </c>
-      <c r="C79" s="11">
-        <f>'balance_raw_20342781'!$C$56</f>
-        <v/>
-      </c>
-      <c r="D79" s="11">
-        <f>'balance_raw_20342781'!$D$56</f>
-        <v/>
-      </c>
-      <c r="E79" s="11">
-        <f>'balance_raw_20342781'!$E$56</f>
-        <v/>
-      </c>
-      <c r="F79" s="11">
-        <f>'balance_raw_20342781'!$F$56</f>
-        <v/>
-      </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" s="12">
-        <f>IFERROR(B79/$B$79*100,"")</f>
-        <v/>
-      </c>
-      <c r="I79" s="12">
-        <f>IFERROR(C79/$B$79*100,"")</f>
-        <v/>
-      </c>
-      <c r="J79" s="12">
-        <f>IFERROR(D79/$B$79*100,"")</f>
-        <v/>
-      </c>
-      <c r="K79" s="12">
-        <f>IFERROR(E79/$B$79*100,"")</f>
-        <v/>
-      </c>
-      <c r="L79" s="12">
-        <f>IFERROR(F79/$B$79*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" ht="22" customHeight="1">
-      <c r="A81" s="3" t="inlineStr">
+      <c r="B82" s="11">
+        <f>'balance_raw_20342781'!$B$59</f>
+        <v/>
+      </c>
+      <c r="C82" s="11">
+        <f>'balance_raw_20342781'!$C$59</f>
+        <v/>
+      </c>
+      <c r="D82" s="11">
+        <f>'balance_raw_20342781'!$D$59</f>
+        <v/>
+      </c>
+      <c r="E82" s="11">
+        <f>'balance_raw_20342781'!$E$59</f>
+        <v/>
+      </c>
+      <c r="F82" s="11">
+        <f>'balance_raw_20342781'!$F$59</f>
+        <v/>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" s="12">
+        <f>IFERROR(B82/$B$82*100,"")</f>
+        <v/>
+      </c>
+      <c r="I82" s="12">
+        <f>IFERROR(C82/$B$82*100,"")</f>
+        <v/>
+      </c>
+      <c r="J82" s="12">
+        <f>IFERROR(D82/$B$82*100,"")</f>
+        <v/>
+      </c>
+      <c r="K82" s="12">
+        <f>IFERROR(E82/$B$82*100,"")</f>
+        <v/>
+      </c>
+      <c r="L82" s="12">
+        <f>IFERROR(F82/$B$82*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>NØGLEOPLYSNINGER</t>
         </is>
       </c>
-      <c r="B81" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C81" s="3" t="n">
+      <c r="B84" s="3" t="n">
         <v>2021</v>
       </c>
-      <c r="D81" s="3" t="n">
+      <c r="C84" s="3" t="n">
         <v>2022</v>
       </c>
-      <c r="E81" s="3" t="n">
+      <c r="D84" s="3" t="n">
         <v>2023</v>
       </c>
-      <c r="F81" s="3" t="n">
+      <c r="E84" s="3" t="n">
         <v>2024</v>
       </c>
-    </row>
-    <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="4" t="inlineStr">
+      <c r="F84" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B82" s="5">
+      <c r="B85" s="8">
         <f>'res_raw_20342781'!$B$19</f>
         <v/>
       </c>
-      <c r="C82" s="5">
+      <c r="C85" s="8">
         <f>'res_raw_20342781'!$C$19</f>
         <v/>
       </c>
-      <c r="D82" s="5">
+      <c r="D85" s="8">
         <f>'res_raw_20342781'!$D$19</f>
         <v/>
       </c>
-      <c r="E82" s="5">
+      <c r="E85" s="8">
         <f>'res_raw_20342781'!$E$19</f>
         <v/>
       </c>
-      <c r="F82" s="5">
+      <c r="F85" s="8">
         <f>'res_raw_20342781'!$F$19</f>
         <v/>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" s="6">
-        <f>IFERROR(B82/$B$82*100,"")</f>
-        <v/>
-      </c>
-      <c r="I82" s="6">
-        <f>IFERROR(C82/$B$82*100,"")</f>
-        <v/>
-      </c>
-      <c r="J82" s="6">
-        <f>IFERROR(D82/$B$82*100,"")</f>
-        <v/>
-      </c>
-      <c r="K82" s="6">
-        <f>IFERROR(E82/$B$82*100,"")</f>
-        <v/>
-      </c>
-      <c r="L82" s="6">
-        <f>IFERROR(F82/$B$82*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="7" t="inlineStr">
-        <is>
-          <t>Investering i materielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B83" s="8">
-        <f>'res_raw_20342781'!$B$20</f>
-        <v/>
-      </c>
-      <c r="C83" s="8">
-        <f>'res_raw_20342781'!$C$20</f>
-        <v/>
-      </c>
-      <c r="D83" s="8">
-        <f>'res_raw_20342781'!$D$20</f>
-        <v/>
-      </c>
-      <c r="E83" s="8">
-        <f>'res_raw_20342781'!$E$20</f>
-        <v/>
-      </c>
-      <c r="F83" s="8">
-        <f>'res_raw_20342781'!$F$20</f>
-        <v/>
-      </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" s="9">
-        <f>IFERROR(B83/$B$83*100,"")</f>
-        <v/>
-      </c>
-      <c r="I83" s="9">
-        <f>IFERROR(C83/$B$83*100,"")</f>
-        <v/>
-      </c>
-      <c r="J83" s="9">
-        <f>IFERROR(D83/$B$83*100,"")</f>
-        <v/>
-      </c>
-      <c r="K83" s="9">
-        <f>IFERROR(E83/$B$83*100,"")</f>
-        <v/>
-      </c>
-      <c r="L83" s="9">
-        <f>IFERROR(F83/$B$83*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="3" t="inlineStr">
-        <is>
-          <t>NØGLETAL</t>
-        </is>
-      </c>
-      <c r="B85" s="3" t="n">
-        <v>2020</v>
-      </c>
-      <c r="C85" s="3" t="n">
-        <v>2021</v>
-      </c>
-      <c r="D85" s="3" t="n">
-        <v>2022</v>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>2024</v>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" s="9">
+        <f>IFERROR(B85/$B$85*100,"")</f>
+        <v/>
+      </c>
+      <c r="I85" s="9">
+        <f>IFERROR(C85/$B$85*100,"")</f>
+        <v/>
+      </c>
+      <c r="J85" s="9">
+        <f>IFERROR(D85/$B$85*100,"")</f>
+        <v/>
+      </c>
+      <c r="K85" s="9">
+        <f>IFERROR(E85/$B$85*100,"")</f>
+        <v/>
+      </c>
+      <c r="L85" s="9">
+        <f>IFERROR(F85/$B$85*100,"")</f>
+        <v/>
       </c>
     </row>
     <row r="86" ht="16" customHeight="1">
       <c r="A86" s="4" t="inlineStr">
         <is>
-          <t>Afkastningsgrad, %</t>
-        </is>
-      </c>
-      <c r="B86" s="13">
-        <f>IFERROR(($B$13+$B$15+$B$14)/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="C86" s="13">
-        <f>IFERROR(($C$13+$C$15+$C$14)/$C$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="D86" s="13">
-        <f>IFERROR(($D$13+$D$15+$D$14)/$D$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="E86" s="13">
-        <f>IFERROR(($E$13+$E$15+$E$14)/$E$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="F86" s="13">
-        <f>IFERROR(($F$13+$F$15+$F$14)/$F$49*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="7" t="inlineStr">
-        <is>
-          <t>Overskudsgrad, %</t>
-        </is>
-      </c>
-      <c r="B87" s="14">
-        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="C87" s="14">
-        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="D87" s="14">
-        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="E87" s="14">
-        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
-        <v/>
-      </c>
-      <c r="F87" s="14">
-        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="4" t="inlineStr">
-        <is>
-          <t>Aktivernes omsætningshastighed, gange</t>
-        </is>
-      </c>
-      <c r="B88" s="13">
-        <f>IFERROR($B$4/$B$49,"")</f>
-        <v/>
-      </c>
-      <c r="C88" s="13">
-        <f>IFERROR($C$4/$C$49,"")</f>
-        <v/>
-      </c>
-      <c r="D88" s="13">
-        <f>IFERROR($D$4/$D$49,"")</f>
-        <v/>
-      </c>
-      <c r="E88" s="13">
-        <f>IFERROR($E$4/$E$49,"")</f>
-        <v/>
-      </c>
-      <c r="F88" s="13">
-        <f>IFERROR($F$4/$F$49,"")</f>
-        <v/>
+          <t>Investering i materielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B86" s="5">
+        <f>'res_raw_20342781'!$B$20</f>
+        <v/>
+      </c>
+      <c r="C86" s="5">
+        <f>'res_raw_20342781'!$C$20</f>
+        <v/>
+      </c>
+      <c r="D86" s="5">
+        <f>'res_raw_20342781'!$D$20</f>
+        <v/>
+      </c>
+      <c r="E86" s="5">
+        <f>'res_raw_20342781'!$E$20</f>
+        <v/>
+      </c>
+      <c r="F86" s="5">
+        <f>'res_raw_20342781'!$F$20</f>
+        <v/>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" s="6">
+        <f>IFERROR(B86/$B$86*100,"")</f>
+        <v/>
+      </c>
+      <c r="I86" s="6">
+        <f>IFERROR(C86/$B$86*100,"")</f>
+        <v/>
+      </c>
+      <c r="J86" s="6">
+        <f>IFERROR(D86/$B$86*100,"")</f>
+        <v/>
+      </c>
+      <c r="K86" s="6">
+        <f>IFERROR(E86/$B$86*100,"")</f>
+        <v/>
+      </c>
+      <c r="L86" s="6">
+        <f>IFERROR(F86/$B$86*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="A88" s="3" t="inlineStr">
+        <is>
+          <t>NØGLETAL</t>
+        </is>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>2025</v>
       </c>
     </row>
     <row r="89" ht="16" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>Egenkapitalens forrentning, %</t>
-        </is>
-      </c>
-      <c r="B89" s="14">
-        <f>IFERROR($B$18/$B$58*100,"")</f>
-        <v/>
-      </c>
-      <c r="C89" s="14">
-        <f>IFERROR($C$18/$C$58*100,"")</f>
-        <v/>
-      </c>
-      <c r="D89" s="14">
-        <f>IFERROR($D$18/$D$58*100,"")</f>
-        <v/>
-      </c>
-      <c r="E89" s="14">
-        <f>IFERROR($E$18/$E$58*100,"")</f>
-        <v/>
-      </c>
-      <c r="F89" s="14">
-        <f>IFERROR($F$18/$F$58*100,"")</f>
+          <t>Afkastningsgrad, %</t>
+        </is>
+      </c>
+      <c r="B89" s="13">
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="C89" s="13">
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="D89" s="13">
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="E89" s="13">
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="F89" s="13">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$52*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="90" ht="16" customHeight="1">
       <c r="A90" s="4" t="inlineStr">
         <is>
-          <t>Gældsrente, %</t>
-        </is>
-      </c>
-      <c r="B90" s="13">
-        <f>IFERROR($B$16/($B$79-$B$58)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C90" s="13">
-        <f>IFERROR($C$16/($C$79-$C$58)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D90" s="13">
-        <f>IFERROR($D$16/($D$79-$D$58)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E90" s="13">
-        <f>IFERROR($E$16/($E$79-$E$58)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F90" s="13">
-        <f>IFERROR($F$16/($F$79-$F$58)*100,"")</f>
+          <t>Overskudsgrad, %</t>
+        </is>
+      </c>
+      <c r="B90" s="14">
+        <f>IFERROR(($B$13+$B$15+$B$14)/$B$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="C90" s="14">
+        <f>IFERROR(($C$13+$C$15+$C$14)/$C$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="D90" s="14">
+        <f>IFERROR(($D$13+$D$15+$D$14)/$D$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="E90" s="14">
+        <f>IFERROR(($E$13+$E$15+$E$14)/$E$4*100,"")</f>
+        <v/>
+      </c>
+      <c r="F90" s="14">
+        <f>IFERROR(($F$13+$F$15+$F$14)/$F$4*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="91" ht="16" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>Soliditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B91" s="14">
-        <f>IFERROR($B$58/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="C91" s="14">
-        <f>IFERROR($C$58/$C$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="D91" s="14">
-        <f>IFERROR($D$58/$D$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="E91" s="14">
-        <f>IFERROR($E$58/$E$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="F91" s="14">
-        <f>IFERROR($F$58/$F$49*100,"")</f>
+          <t>Aktivernes omsætningshastighed, gange</t>
+        </is>
+      </c>
+      <c r="B91" s="13">
+        <f>IFERROR($B$4/$B$52,"")</f>
+        <v/>
+      </c>
+      <c r="C91" s="13">
+        <f>IFERROR($C$4/$C$52,"")</f>
+        <v/>
+      </c>
+      <c r="D91" s="13">
+        <f>IFERROR($D$4/$D$52,"")</f>
+        <v/>
+      </c>
+      <c r="E91" s="13">
+        <f>IFERROR($E$4/$E$52,"")</f>
+        <v/>
+      </c>
+      <c r="F91" s="13">
+        <f>IFERROR($F$4/$F$52,"")</f>
         <v/>
       </c>
     </row>
     <row r="92" ht="16" customHeight="1">
       <c r="A92" s="4" t="inlineStr">
         <is>
-          <t>Gearing</t>
-        </is>
-      </c>
-      <c r="B92" s="13">
-        <f>IFERROR(($B$79-$B$58)/$B$58,"")</f>
-        <v/>
-      </c>
-      <c r="C92" s="13">
-        <f>IFERROR(($C$79-$C$58)/$C$58,"")</f>
-        <v/>
-      </c>
-      <c r="D92" s="13">
-        <f>IFERROR(($D$79-$D$58)/$D$58,"")</f>
-        <v/>
-      </c>
-      <c r="E92" s="13">
-        <f>IFERROR(($E$79-$E$58)/$E$58,"")</f>
-        <v/>
-      </c>
-      <c r="F92" s="13">
-        <f>IFERROR(($F$79-$F$58)/$F$58,"")</f>
+          <t>Egenkapitalens forrentning, %</t>
+        </is>
+      </c>
+      <c r="B92" s="14">
+        <f>IFERROR($B$18/$B$61*100,"")</f>
+        <v/>
+      </c>
+      <c r="C92" s="14">
+        <f>IFERROR($C$18/$C$61*100,"")</f>
+        <v/>
+      </c>
+      <c r="D92" s="14">
+        <f>IFERROR($D$18/$D$61*100,"")</f>
+        <v/>
+      </c>
+      <c r="E92" s="14">
+        <f>IFERROR($E$18/$E$61*100,"")</f>
+        <v/>
+      </c>
+      <c r="F92" s="14">
+        <f>IFERROR($F$18/$F$61*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>Likviditetsgrad, %</t>
-        </is>
-      </c>
-      <c r="B93" s="14">
-        <f>IFERROR($B$48/$B$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="C93" s="14">
-        <f>IFERROR($C$48/$C$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="D93" s="14">
-        <f>IFERROR($D$48/$D$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="E93" s="14">
-        <f>IFERROR($E$48/$E$77*100,"")</f>
-        <v/>
-      </c>
-      <c r="F93" s="14">
-        <f>IFERROR($F$48/$F$77*100,"")</f>
+          <t>Gældsrente, %</t>
+        </is>
+      </c>
+      <c r="B93" s="13">
+        <f>IFERROR($B$16/($B$82-$B$61)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C93" s="13">
+        <f>IFERROR($C$16/($C$82-$C$61)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D93" s="13">
+        <f>IFERROR($D$16/($D$82-$D$61)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E93" s="13">
+        <f>IFERROR($E$16/($E$82-$E$61)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F93" s="13">
+        <f>IFERROR($F$16/($F$82-$F$61)*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="94" ht="16" customHeight="1">
       <c r="A94" s="4" t="inlineStr">
         <is>
-          <t>Rentemarginal, %</t>
-        </is>
-      </c>
-      <c r="B94" s="13">
-        <f>IFERROR(B86-B90,"")</f>
-        <v/>
-      </c>
-      <c r="C94" s="13">
-        <f>IFERROR(C86-C90,"")</f>
-        <v/>
-      </c>
-      <c r="D94" s="13">
-        <f>IFERROR(D86-D90,"")</f>
-        <v/>
-      </c>
-      <c r="E94" s="13">
-        <f>IFERROR(E86-E90,"")</f>
-        <v/>
-      </c>
-      <c r="F94" s="13">
-        <f>IFERROR(F86-F90,"")</f>
+          <t>Soliditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B94" s="14">
+        <f>IFERROR($B$61/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="C94" s="14">
+        <f>IFERROR($C$61/$C$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="D94" s="14">
+        <f>IFERROR($D$61/$D$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="E94" s="14">
+        <f>IFERROR($E$61/$E$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="F94" s="14">
+        <f>IFERROR($F$61/$F$52*100,"")</f>
         <v/>
       </c>
     </row>
     <row r="95" ht="16" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>Gældsandel, %</t>
-        </is>
-      </c>
-      <c r="B95" s="14">
-        <f>IFERROR(($B$79-$B$58)/$B$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="C95" s="14">
-        <f>IFERROR(($C$79-$C$58)/$C$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="D95" s="14">
-        <f>IFERROR(($D$79-$D$58)/$D$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="E95" s="14">
-        <f>IFERROR(($E$79-$E$58)/$E$49*100,"")</f>
-        <v/>
-      </c>
-      <c r="F95" s="14">
-        <f>IFERROR(($F$79-$F$58)/$F$49*100,"")</f>
+          <t>Gearing</t>
+        </is>
+      </c>
+      <c r="B95" s="13">
+        <f>IFERROR(($B$82-$B$61)/$B$61,"")</f>
+        <v/>
+      </c>
+      <c r="C95" s="13">
+        <f>IFERROR(($C$82-$C$61)/$C$61,"")</f>
+        <v/>
+      </c>
+      <c r="D95" s="13">
+        <f>IFERROR(($D$82-$D$61)/$D$61,"")</f>
+        <v/>
+      </c>
+      <c r="E95" s="13">
+        <f>IFERROR(($E$82-$E$61)/$E$61,"")</f>
+        <v/>
+      </c>
+      <c r="F95" s="13">
+        <f>IFERROR(($F$82-$F$61)/$F$61,"")</f>
         <v/>
       </c>
     </row>
     <row r="96" ht="16" customHeight="1">
       <c r="A96" s="4" t="inlineStr">
         <is>
+          <t>Likviditetsgrad, %</t>
+        </is>
+      </c>
+      <c r="B96" s="14">
+        <f>IFERROR($B$51/$B$80*100,"")</f>
+        <v/>
+      </c>
+      <c r="C96" s="14">
+        <f>IFERROR($C$51/$C$80*100,"")</f>
+        <v/>
+      </c>
+      <c r="D96" s="14">
+        <f>IFERROR($D$51/$D$80*100,"")</f>
+        <v/>
+      </c>
+      <c r="E96" s="14">
+        <f>IFERROR($E$51/$E$80*100,"")</f>
+        <v/>
+      </c>
+      <c r="F96" s="14">
+        <f>IFERROR($F$51/$F$80*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="7" t="inlineStr">
+        <is>
+          <t>Rentemarginal, %</t>
+        </is>
+      </c>
+      <c r="B97" s="13">
+        <f>IFERROR(B89-B93,"")</f>
+        <v/>
+      </c>
+      <c r="C97" s="13">
+        <f>IFERROR(C89-C93,"")</f>
+        <v/>
+      </c>
+      <c r="D97" s="13">
+        <f>IFERROR(D89-D93,"")</f>
+        <v/>
+      </c>
+      <c r="E97" s="13">
+        <f>IFERROR(E89-E93,"")</f>
+        <v/>
+      </c>
+      <c r="F97" s="13">
+        <f>IFERROR(F89-F93,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>Gældsandel, %</t>
+        </is>
+      </c>
+      <c r="B98" s="14">
+        <f>IFERROR(($B$82-$B$61)/$B$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="C98" s="14">
+        <f>IFERROR(($C$82-$C$61)/$C$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="D98" s="14">
+        <f>IFERROR(($D$82-$D$61)/$D$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="E98" s="14">
+        <f>IFERROR(($E$82-$E$61)/$E$52*100,"")</f>
+        <v/>
+      </c>
+      <c r="F98" s="14">
+        <f>IFERROR(($F$82-$F$61)/$F$52*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="7" t="inlineStr">
+        <is>
           <t>Kapitalbindingsgrad, %</t>
         </is>
       </c>
-      <c r="B96" s="13">
-        <f>IFERROR($B$33/($B$58+$B$65)*100,"")</f>
-        <v/>
-      </c>
-      <c r="C96" s="13">
-        <f>IFERROR($C$33/($C$58+$C$65)*100,"")</f>
-        <v/>
-      </c>
-      <c r="D96" s="13">
-        <f>IFERROR($D$33/($D$58+$D$65)*100,"")</f>
-        <v/>
-      </c>
-      <c r="E96" s="13">
-        <f>IFERROR($E$33/($E$58+$E$65)*100,"")</f>
-        <v/>
-      </c>
-      <c r="F96" s="13">
-        <f>IFERROR($F$33/($F$58+$F$65)*100,"")</f>
+      <c r="B99" s="13">
+        <f>IFERROR($B$36/($B$61+$B$68)*100,"")</f>
+        <v/>
+      </c>
+      <c r="C99" s="13">
+        <f>IFERROR($C$36/($C$61+$C$68)*100,"")</f>
+        <v/>
+      </c>
+      <c r="D99" s="13">
+        <f>IFERROR($D$36/($D$61+$D$68)*100,"")</f>
+        <v/>
+      </c>
+      <c r="E99" s="13">
+        <f>IFERROR($E$36/($E$61+$E$68)*100,"")</f>
+        <v/>
+      </c>
+      <c r="F99" s="13">
+        <f>IFERROR($F$36/($F$61+$F$68)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B102" s="17">
+        <f>'pengestrom_raw_20342781'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C102" s="17">
+        <f>'pengestrom_raw_20342781'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D102" s="17">
+        <f>'pengestrom_raw_20342781'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E102" s="17">
+        <f>'pengestrom_raw_20342781'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F102" s="17">
+        <f>'pengestrom_raw_20342781'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B103" s="17">
+        <f>'pengestrom_raw_20342781'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C103" s="17">
+        <f>'pengestrom_raw_20342781'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D103" s="17">
+        <f>'pengestrom_raw_20342781'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E103" s="17">
+        <f>'pengestrom_raw_20342781'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F103" s="17">
+        <f>'pengestrom_raw_20342781'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B104" s="17">
+        <f>'pengestrom_raw_20342781'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C104" s="17">
+        <f>'pengestrom_raw_20342781'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D104" s="17">
+        <f>'pengestrom_raw_20342781'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E104" s="17">
+        <f>'pengestrom_raw_20342781'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F104" s="17">
+        <f>'pengestrom_raw_20342781'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B105" s="17">
+        <f>'pengestrom_raw_20342781'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C105" s="17">
+        <f>'pengestrom_raw_20342781'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D105" s="17">
+        <f>'pengestrom_raw_20342781'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E105" s="17">
+        <f>'pengestrom_raw_20342781'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F105" s="17">
+        <f>'pengestrom_raw_20342781'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B106">
+        <f>IF(ABS(('pengestrom_raw_20342781'!$B$2+'pengestrom_raw_20342781'!$B$3+'pengestrom_raw_20342781'!$B$4)-'pengestrom_raw_20342781'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_20342781'!$B$2+'pengestrom_raw_20342781'!$B$3+'pengestrom_raw_20342781'!$B$4)-'pengestrom_raw_20342781'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C106">
+        <f>IF(ABS(('pengestrom_raw_20342781'!$C$2+'pengestrom_raw_20342781'!$C$3+'pengestrom_raw_20342781'!$C$4)-'pengestrom_raw_20342781'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_20342781'!$C$2+'pengestrom_raw_20342781'!$C$3+'pengestrom_raw_20342781'!$C$4)-'pengestrom_raw_20342781'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D106">
+        <f>IF(ABS(('pengestrom_raw_20342781'!$D$2+'pengestrom_raw_20342781'!$D$3+'pengestrom_raw_20342781'!$D$4)-'pengestrom_raw_20342781'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_20342781'!$D$2+'pengestrom_raw_20342781'!$D$3+'pengestrom_raw_20342781'!$D$4)-'pengestrom_raw_20342781'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E106">
+        <f>IF(ABS(('pengestrom_raw_20342781'!$E$2+'pengestrom_raw_20342781'!$E$3+'pengestrom_raw_20342781'!$E$4)-'pengestrom_raw_20342781'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_20342781'!$E$2+'pengestrom_raw_20342781'!$E$3+'pengestrom_raw_20342781'!$E$4)-'pengestrom_raw_20342781'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F106">
+        <f>IF(ABS(('pengestrom_raw_20342781'!$F$2+'pengestrom_raw_20342781'!$F$3+'pengestrom_raw_20342781'!$F$4)-'pengestrom_raw_20342781'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_20342781'!$F$2+'pengestrom_raw_20342781'!$F$3+'pengestrom_raw_20342781'!$F$4)-'pengestrom_raw_20342781'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4706,403 +4993,403 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>24767</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>148384</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>500231</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>733382</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>764561</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>753144</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>60890</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>3776</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>3118</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>125</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>1205</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>31253</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>100089</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>389803</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>585067</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>606632</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>580086</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>37284</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>29979</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>47483</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>59696</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>64182</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>73085</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>-6486</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>48296</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>110429</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>148315</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>157929</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>173058</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>59901</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>32684</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>43563</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>53902</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>58428</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>65674</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>2539</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>2217</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>1913</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>1016</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>2971</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>6882</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>-42781</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>-10591</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>22500</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>34842</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>36523</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>27417</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n">
-        <v>-794</v>
-      </c>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>-43</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>-1377</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>-39</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>-19</v>
       </c>
+      <c r="F12" s="17" t="n">
+        <v>-21</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>2394</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>7810</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>2519</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>19126</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>20566</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>9921</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>6912</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>4406</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>21288</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>5723</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>5589</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>5594</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>-2139</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>4813</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>-17128</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>16628</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>19080</v>
       </c>
+      <c r="F15" s="17" t="n">
+        <v>8134</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>-48253</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>-8037</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>2081</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>50416</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>52613</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>35529</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>-8376</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>-1802</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>724</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>11021</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>11509</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>7982</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>-39876</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>-6236</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>1357</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>39395</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>41104</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>27547</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>135</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>75</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>84</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>105</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>112</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>121</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5115,7 +5402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="72" customWidth="1" min="1" max="1"/>
@@ -5133,999 +5420,1033 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
-        <is>
-          <t>Immaterielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B2" s="16" t="n">
-        <v>3996</v>
-      </c>
-      <c r="C2" s="16" t="n">
-        <v>3029</v>
-      </c>
-      <c r="D2" s="16" t="n">
-        <v>1641</v>
-      </c>
-      <c r="E2" s="16" t="n">
-        <v>7422</v>
-      </c>
-      <c r="F2" s="16" t="n">
-        <v>17209</v>
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Udviklingsprojekter</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n"/>
+      <c r="C2" s="17" t="n"/>
+      <c r="D2" s="17" t="n"/>
+      <c r="E2" s="17" t="n"/>
+      <c r="F2" s="17" t="n">
+        <v>19129</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
-        <is>
-          <t>Grunde og bygninger</t>
-        </is>
-      </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Patenter, varemærker mv.</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
-        <is>
-          <t>Produktionsanlæg og maskiner</t>
-        </is>
-      </c>
-      <c r="B4" s="16" t="n"/>
-      <c r="C4" s="16" t="n"/>
-      <c r="D4" s="16" t="n"/>
-      <c r="E4" s="16" t="n"/>
-      <c r="F4" s="16" t="n"/>
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n"/>
+      <c r="C4" s="17" t="n"/>
+      <c r="D4" s="17" t="n"/>
+      <c r="E4" s="17" t="n"/>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
+          <t>Immaterielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
+        <v>3029</v>
+      </c>
+      <c r="C5" s="17" t="n">
+        <v>1641</v>
+      </c>
+      <c r="D5" s="17" t="n">
+        <v>7422</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>17209</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>19129</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Grunde og bygninger</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n"/>
+      <c r="F6" s="17" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Produktionsanlæg og maskiner</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="inlineStr">
+        <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>1363</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B8" s="17" t="n">
         <v>1329</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C8" s="17" t="n">
         <v>1367</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D8" s="17" t="n">
         <v>1828</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E8" s="17" t="n">
         <v>2006</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="F8" s="17" t="n">
+        <v>2224</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>343</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>282</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>230</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>282</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>629</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="F9" s="17" t="n">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n"/>
-      <c r="C7" s="16" t="n"/>
-      <c r="D7" s="16" t="n"/>
-      <c r="E7" s="16" t="n"/>
-      <c r="F7" s="16" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="B10" s="17" t="n"/>
+      <c r="C10" s="17" t="n"/>
+      <c r="D10" s="17" t="n"/>
+      <c r="E10" s="17" t="n"/>
+      <c r="F10" s="17" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n">
-        <v>1707</v>
-      </c>
-      <c r="C8" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>1611</v>
       </c>
-      <c r="D8" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>1598</v>
       </c>
-      <c r="E8" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>2110</v>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>2635</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="F11" s="17" t="n">
+        <v>3301</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>1844</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B12" s="17" t="n">
         <v>1908</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C12" s="17" t="n">
         <v>630</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <v>557</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <v>535</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="F12" s="17" t="n">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>1978</v>
       </c>
-      <c r="C10" s="16" t="n">
-        <v>1978</v>
-      </c>
-      <c r="D10" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>2048</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>2251</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>2322</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
-        <is>
-          <t>Finansielle anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="n">
-        <v>3822</v>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>3886</v>
-      </c>
-      <c r="D11" s="16" t="n">
-        <v>2678</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>2808</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>2856</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>Anlægsaktiver</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n">
-        <v>9524</v>
-      </c>
-      <c r="C12" s="16" t="n">
-        <v>8526</v>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>5917</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>12340</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>22701</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Råvarer og hjælpematerialer</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="F13" s="17" t="n">
+        <v>2395</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Varer under fremstilling</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n"/>
-      <c r="C14" s="16" t="n"/>
-      <c r="D14" s="16" t="n"/>
-      <c r="E14" s="16" t="n"/>
-      <c r="F14" s="16" t="n"/>
+          <t>Finansielle anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="n">
+        <v>3886</v>
+      </c>
+      <c r="C14" s="17" t="n">
+        <v>2678</v>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>2808</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>2856</v>
+      </c>
+      <c r="F14" s="17" t="n">
+        <v>23400</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
+          <t>Anlægsaktiver</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>8526</v>
+      </c>
+      <c r="C15" s="17" t="n">
+        <v>5917</v>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>12340</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>22701</v>
+      </c>
+      <c r="F15" s="17" t="n">
+        <v>45830</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Råvarer og hjælpematerialer</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="17" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Varer under fremstilling</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
           <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>1065</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>1054</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>875</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>773</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>707</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>Varebeholdninger</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="n">
-        <v>1065</v>
-      </c>
-      <c r="C16" s="16" t="n">
-        <v>1054</v>
-      </c>
-      <c r="D16" s="16" t="n">
-        <v>875</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>773</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Tilgodehavender fra salg og tjenesteydelser</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Tilgodehavender hos tilknyttede virksomheder</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
+      <c r="F18" s="17" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
+          <t>Varebeholdninger</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="n">
+        <v>1054</v>
+      </c>
+      <c r="C19" s="17" t="n">
+        <v>875</v>
+      </c>
+      <c r="D19" s="17" t="n">
+        <v>773</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>707</v>
+      </c>
+      <c r="F19" s="17" t="n">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t>Tilgodehavender fra salg og tjenesteydelser</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>Tilgodehavender hos tilknyttede virksomheder</t>
+        </is>
+      </c>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="inlineStr">
+        <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>8570</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B22" s="17" t="n">
         <v>7339</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C22" s="17" t="n">
         <v>6520</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D22" s="17" t="n">
         <v>15127</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E22" s="17" t="n">
         <v>10443</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="F22" s="17" t="n">
+        <v>5018</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>60332</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>60291</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>104318</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>109748</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>120618</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="F23" s="17" t="n">
+        <v>95433</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="inlineStr">
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="n"/>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
-        <v>1111</v>
-      </c>
-      <c r="C23" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>4410</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="C26" s="17" t="n">
         <v>3686</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="16" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
-        <v>163370</v>
-      </c>
-      <c r="C24" s="16" t="n">
+      <c r="B27" s="17" t="n">
         <v>170237</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>203893</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>214187</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>223205</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="F27" s="17" t="n">
+        <v>159472</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="n"/>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="inlineStr">
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="n"/>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n">
+        <v>117088</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
-        <v>106710</v>
-      </c>
-      <c r="C26" s="16" t="n">
+      <c r="B29" s="17" t="n">
         <v>139441</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="C29" s="17" t="n">
         <v>163802</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="D29" s="17" t="n">
         <v>173499</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="E29" s="17" t="n">
         <v>177942</v>
       </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>Omsætningsaktiver</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="n">
-        <v>271145</v>
-      </c>
-      <c r="C27" s="16" t="n">
-        <v>310731</v>
-      </c>
-      <c r="D27" s="16" t="n">
-        <v>368570</v>
-      </c>
-      <c r="E27" s="16" t="n">
-        <v>388460</v>
-      </c>
-      <c r="F27" s="16" t="n">
-        <v>401854</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>Aktiver</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="n">
-        <v>280669</v>
-      </c>
-      <c r="C28" s="16" t="n">
-        <v>319257</v>
-      </c>
-      <c r="D28" s="16" t="n">
-        <v>374487</v>
-      </c>
-      <c r="E28" s="16" t="n">
-        <v>400800</v>
-      </c>
-      <c r="F28" s="16" t="n">
-        <v>424555</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>Selskabskapital</t>
-        </is>
-      </c>
-      <c r="B29" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C29" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D29" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E29" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F29" s="16" t="n">
-        <v>1000</v>
+      <c r="F29" s="17" t="n">
+        <v>78965</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="15" t="inlineStr">
         <is>
-          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
-        </is>
-      </c>
-      <c r="B30" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
+          <t>Omsætningsaktiver</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="n">
+        <v>310731</v>
+      </c>
+      <c r="C30" s="17" t="n">
+        <v>368570</v>
+      </c>
+      <c r="D30" s="17" t="n">
+        <v>388460</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>401854</v>
+      </c>
+      <c r="F30" s="17" t="n">
+        <v>356113</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
+          <t>Aktiver</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="n">
+        <v>319257</v>
+      </c>
+      <c r="C31" s="17" t="n">
+        <v>374487</v>
+      </c>
+      <c r="D31" s="17" t="n">
+        <v>400800</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>424555</v>
+      </c>
+      <c r="F31" s="17" t="n">
+        <v>401943</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Selskabskapital</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C32" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D32" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F32" s="17" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>Reserve for nettoopskrivning (indre værdis metode)</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="n"/>
+      <c r="F33" s="17" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="n"/>
+      <c r="F34" s="17" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="n"/>
+      <c r="F35" s="17" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="n"/>
-      <c r="F33" s="16" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="n"/>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
-        <v>39135</v>
-      </c>
-      <c r="C34" s="16" t="n">
+      <c r="B37" s="17" t="n">
         <v>32948</v>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="C37" s="17" t="n">
         <v>34404</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="D37" s="17" t="n">
         <v>61800</v>
       </c>
-      <c r="F34" s="16" t="n">
+      <c r="E37" s="17" t="n">
         <v>82903</v>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>Egenkapital i alt</t>
-        </is>
-      </c>
-      <c r="B35" s="16" t="n">
-        <v>39405</v>
-      </c>
-      <c r="C35" s="16" t="n">
-        <v>34972</v>
-      </c>
-      <c r="D35" s="16" t="n">
-        <v>35061</v>
-      </c>
-      <c r="E35" s="16" t="n">
-        <v>61532</v>
-      </c>
-      <c r="F35" s="16" t="n">
-        <v>109174</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="inlineStr">
-        <is>
-          <t>Hensættelse til udskudt skat</t>
-        </is>
-      </c>
-      <c r="B36" s="16" t="n">
-        <v>1981</v>
-      </c>
-      <c r="C36" s="16" t="n">
-        <v>4392</v>
-      </c>
-      <c r="D36" s="16" t="n">
-        <v>8341</v>
-      </c>
-      <c r="E36" s="16" t="n">
-        <v>12499</v>
-      </c>
-      <c r="F36" s="16" t="n">
-        <v>9407</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t>Hensatte forpligtelser</t>
-        </is>
-      </c>
-      <c r="B37" s="16" t="n">
-        <v>1981</v>
-      </c>
-      <c r="C37" s="16" t="n">
-        <v>4392</v>
-      </c>
-      <c r="D37" s="16" t="n">
-        <v>8341</v>
-      </c>
-      <c r="E37" s="16" t="n">
-        <v>12499</v>
-      </c>
-      <c r="F37" s="16" t="n">
-        <v>9407</v>
+      <c r="F37" s="17" t="n">
+        <v>110454</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>Ansvarlig lånekapital (langfristet)</t>
-        </is>
-      </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
+          <t>Egenkapital i alt</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="n">
+        <v>34972</v>
+      </c>
+      <c r="C38" s="17" t="n">
+        <v>35061</v>
+      </c>
+      <c r="D38" s="17" t="n">
+        <v>61532</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>109174</v>
+      </c>
+      <c r="F38" s="17" t="n">
+        <v>102344</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>Langfristede lån</t>
-        </is>
-      </c>
-      <c r="B39" s="16" t="n">
-        <v>70000</v>
-      </c>
-      <c r="C39" s="16" t="n">
-        <v>38533</v>
-      </c>
-      <c r="D39" s="16" t="n">
-        <v>26866</v>
-      </c>
-      <c r="E39" s="16" t="n">
-        <v>15199</v>
-      </c>
-      <c r="F39" s="16" t="n">
-        <v>3532</v>
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>Hensættelse til udskudt skat</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="n">
+        <v>4392</v>
+      </c>
+      <c r="C39" s="17" t="n">
+        <v>8341</v>
+      </c>
+      <c r="D39" s="17" t="n">
+        <v>12499</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>9407</v>
+      </c>
+      <c r="F39" s="17" t="n">
+        <v>12524</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
+          <t>Hensatte forpligtelser</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="n">
+        <v>4392</v>
+      </c>
+      <c r="C40" s="17" t="n">
+        <v>8341</v>
+      </c>
+      <c r="D40" s="17" t="n">
+        <v>12499</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>9407</v>
+      </c>
+      <c r="F40" s="17" t="n">
+        <v>12524</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (langfristet)</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="n"/>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="inlineStr">
+        <is>
+          <t>Langfristede lån</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="n">
+        <v>38533</v>
+      </c>
+      <c r="C42" s="17" t="n">
+        <v>26866</v>
+      </c>
+      <c r="D42" s="17" t="n">
+        <v>15199</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>3532</v>
+      </c>
+      <c r="F42" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="inlineStr">
+        <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="n"/>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="inlineStr">
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="n"/>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>Langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B42" s="16" t="n">
-        <v>125261</v>
-      </c>
-      <c r="C42" s="16" t="n">
-        <v>106574</v>
-      </c>
-      <c r="D42" s="16" t="n">
-        <v>82454</v>
-      </c>
-      <c r="E42" s="16" t="n">
-        <v>58468</v>
-      </c>
-      <c r="F42" s="16" t="n">
-        <v>34480</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="15" t="inlineStr">
-        <is>
-          <t>Ansvarlig lånekapital (kortfristet)</t>
-        </is>
-      </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr">
-        <is>
-          <t>Kortfristet del af langfristede gældsforpligtelser</t>
-        </is>
-      </c>
-      <c r="B44" s="16" t="n">
-        <v>14489</v>
-      </c>
-      <c r="C44" s="16" t="n">
-        <v>31467</v>
-      </c>
-      <c r="D44" s="16" t="n">
-        <v>24167</v>
-      </c>
-      <c r="E44" s="16" t="n">
-        <v>24167</v>
-      </c>
-      <c r="F44" s="16" t="n"/>
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="n"/>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
         <is>
+          <t>Langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B45" s="17" t="n">
+        <v>106574</v>
+      </c>
+      <c r="C45" s="17" t="n">
+        <v>82454</v>
+      </c>
+      <c r="D45" s="17" t="n">
+        <v>58468</v>
+      </c>
+      <c r="E45" s="17" t="n">
+        <v>34480</v>
+      </c>
+      <c r="F45" s="17" t="n">
+        <v>18668</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>Ansvarlig lånekapital (kortfristet)</t>
+        </is>
+      </c>
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="n"/>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="inlineStr">
+        <is>
+          <t>Kortfristet del af langfristede gældsforpligtelser</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="n">
+        <v>31467</v>
+      </c>
+      <c r="C47" s="17" t="n">
+        <v>24167</v>
+      </c>
+      <c r="D47" s="17" t="n">
+        <v>24167</v>
+      </c>
+      <c r="E47" s="17" t="n"/>
+      <c r="F47" s="17" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="inlineStr">
+        <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n">
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n">
         <v>24167</v>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="F48" s="17" t="n">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="n"/>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="B49" s="17" t="n"/>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n">
-        <v>3631</v>
-      </c>
-      <c r="C47" s="16" t="n">
+      <c r="B50" s="17" t="n">
         <v>5170</v>
       </c>
-      <c r="D47" s="16" t="n">
+      <c r="C50" s="17" t="n">
         <v>16946</v>
       </c>
-      <c r="E47" s="16" t="n">
+      <c r="D50" s="17" t="n">
         <v>21410</v>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="E50" s="17" t="n">
         <v>16612</v>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="F50" s="17" t="n">
+        <v>15199</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="B51" s="17" t="n"/>
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="17" t="n"/>
+      <c r="E51" s="17" t="n"/>
+      <c r="F51" s="17" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n"/>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="B52" s="17" t="n"/>
+      <c r="C52" s="17" t="n"/>
+      <c r="D52" s="17" t="n"/>
+      <c r="E52" s="17" t="n"/>
+      <c r="F52" s="17" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n">
+      <c r="B53" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C50" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="16" t="n"/>
-      <c r="E50" s="16" t="n">
+      <c r="C53" s="17" t="n"/>
+      <c r="D53" s="17" t="n">
         <v>6725</v>
       </c>
-      <c r="F50" s="16" t="n">
+      <c r="E53" s="17" t="n">
         <v>14456</v>
       </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="F53" s="17" t="n">
+        <v>4573</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n"/>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="16" t="n"/>
-      <c r="E51" s="16" t="n"/>
-      <c r="F51" s="16" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="B54" s="17" t="n"/>
+      <c r="C54" s="17" t="n"/>
+      <c r="D54" s="17" t="n"/>
+      <c r="E54" s="17" t="n"/>
+      <c r="F54" s="17" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n">
-        <v>34068</v>
-      </c>
-      <c r="C52" s="16" t="n">
+      <c r="B55" s="17" t="n">
         <v>18323</v>
       </c>
-      <c r="D52" s="16" t="n">
+      <c r="C55" s="17" t="n">
         <v>17254</v>
       </c>
-      <c r="E52" s="16" t="n">
+      <c r="D55" s="17" t="n">
         <v>30127</v>
       </c>
-      <c r="F52" s="16" t="n">
+      <c r="E55" s="17" t="n">
         <v>27169</v>
       </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="F55" s="17" t="n">
+        <v>40338</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B53" s="16" t="n">
-        <v>59262</v>
-      </c>
-      <c r="C53" s="16" t="n">
+      <c r="B56" s="17" t="n">
         <v>117471</v>
       </c>
-      <c r="D53" s="16" t="n">
+      <c r="C56" s="17" t="n">
         <v>186718</v>
       </c>
-      <c r="E53" s="16" t="n">
+      <c r="D56" s="17" t="n">
         <v>181762</v>
       </c>
-      <c r="F53" s="16" t="n">
+      <c r="E56" s="17" t="n">
         <v>189090</v>
       </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="17" t="inlineStr">
+      <c r="F56" s="17" t="n">
+        <v>195797</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B54" s="16" t="n">
-        <v>114022</v>
-      </c>
-      <c r="C54" s="16" t="n">
+      <c r="B57" s="17" t="n">
         <v>173320</v>
       </c>
-      <c r="D54" s="16" t="n">
+      <c r="C57" s="17" t="n">
         <v>248630</v>
       </c>
-      <c r="E54" s="16" t="n">
+      <c r="D57" s="17" t="n">
         <v>268301</v>
       </c>
-      <c r="F54" s="16" t="n">
+      <c r="E57" s="17" t="n">
         <v>271494</v>
       </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="17" t="inlineStr">
+      <c r="F57" s="17" t="n">
+        <v>268406</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B55" s="16" t="n">
-        <v>239283</v>
-      </c>
-      <c r="C55" s="16" t="n">
+      <c r="B58" s="17" t="n">
         <v>279894</v>
       </c>
-      <c r="D55" s="16" t="n">
+      <c r="C58" s="17" t="n">
         <v>331085</v>
       </c>
-      <c r="E55" s="16" t="n">
+      <c r="D58" s="17" t="n">
         <v>326769</v>
       </c>
-      <c r="F55" s="16" t="n">
+      <c r="E58" s="17" t="n">
         <v>305974</v>
       </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="17" t="inlineStr">
+      <c r="F58" s="17" t="n">
+        <v>287075</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B56" s="16" t="n">
-        <v>280669</v>
-      </c>
-      <c r="C56" s="16" t="n">
+      <c r="B59" s="17" t="n">
         <v>319257</v>
       </c>
-      <c r="D56" s="16" t="n">
+      <c r="C59" s="17" t="n">
         <v>374487</v>
       </c>
-      <c r="E56" s="16" t="n">
+      <c r="D59" s="17" t="n">
         <v>400800</v>
       </c>
-      <c r="F56" s="16" t="n">
+      <c r="E59" s="17" t="n">
         <v>424555</v>
+      </c>
+      <c r="F59" s="17" t="n">
+        <v>401943</v>
       </c>
     </row>
   </sheetData>
@@ -6134,6 +6455,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>52588</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>47686</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>41120</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>53764</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>63443</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-7764</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>16154</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-16481</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-26377</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-959</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-18688</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-24119</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-23986</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-35988</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-35812</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6164,13 +6607,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6502,15 +6945,15 @@
         </is>
       </c>
       <c r="B19" s="24">
-        <f>'balance_raw_20342781'!$F$12</f>
+        <f>'balance_raw_20342781'!$F$15</f>
         <v/>
       </c>
       <c r="C19" s="24">
-        <f>'balance_raw_20342781'!$E$12</f>
+        <f>'balance_raw_20342781'!$E$15</f>
         <v/>
       </c>
       <c r="D19" s="24">
-        <f>'balance_raw_20342781'!$D$12</f>
+        <f>'balance_raw_20342781'!$D$15</f>
         <v/>
       </c>
       <c r="F19" s="25" t="inlineStr">
@@ -6526,15 +6969,15 @@
         </is>
       </c>
       <c r="B20" s="24">
-        <f>'balance_raw_20342781'!$F$27</f>
+        <f>'balance_raw_20342781'!$F$30</f>
         <v/>
       </c>
       <c r="C20" s="24">
-        <f>'balance_raw_20342781'!$E$27</f>
+        <f>'balance_raw_20342781'!$E$30</f>
         <v/>
       </c>
       <c r="D20" s="24">
-        <f>'balance_raw_20342781'!$D$27</f>
+        <f>'balance_raw_20342781'!$D$30</f>
         <v/>
       </c>
       <c r="F20" s="25" t="inlineStr">
@@ -6581,15 +7024,15 @@
         </is>
       </c>
       <c r="B23" s="24">
-        <f>'balance_raw_20342781'!$F$35</f>
+        <f>'balance_raw_20342781'!$F$38</f>
         <v/>
       </c>
       <c r="C23" s="24">
-        <f>'balance_raw_20342781'!$E$35</f>
+        <f>'balance_raw_20342781'!$E$38</f>
         <v/>
       </c>
       <c r="D23" s="24">
-        <f>'balance_raw_20342781'!$D$35</f>
+        <f>'balance_raw_20342781'!$D$38</f>
         <v/>
       </c>
       <c r="F23" s="25" t="inlineStr">
@@ -6605,15 +7048,15 @@
         </is>
       </c>
       <c r="B24" s="24">
-        <f>'balance_raw_20342781'!$F$56-'balance_raw_20342781'!$F$35</f>
+        <f>'balance_raw_20342781'!$F$59-'balance_raw_20342781'!$F$38</f>
         <v/>
       </c>
       <c r="C24" s="24">
-        <f>'balance_raw_20342781'!$E$56-'balance_raw_20342781'!$E$35</f>
+        <f>'balance_raw_20342781'!$E$59-'balance_raw_20342781'!$E$38</f>
         <v/>
       </c>
       <c r="D24" s="24">
-        <f>'balance_raw_20342781'!$D$56-'balance_raw_20342781'!$D$35</f>
+        <f>'balance_raw_20342781'!$D$59-'balance_raw_20342781'!$D$38</f>
         <v/>
       </c>
       <c r="F24" s="25" t="inlineStr">
@@ -6671,15 +7114,15 @@
         </is>
       </c>
       <c r="B28" s="24">
-        <f>'balance_raw_20342781'!$F$16</f>
+        <f>'balance_raw_20342781'!$F$19</f>
         <v/>
       </c>
       <c r="C28" s="24">
-        <f>'balance_raw_20342781'!$E$16</f>
+        <f>'balance_raw_20342781'!$E$19</f>
         <v/>
       </c>
       <c r="D28" s="24">
-        <f>'balance_raw_20342781'!$D$16</f>
+        <f>'balance_raw_20342781'!$D$19</f>
         <v/>
       </c>
       <c r="F28" s="25" t="inlineStr">
@@ -6695,15 +7138,15 @@
         </is>
       </c>
       <c r="B29" s="24">
-        <f>'balance_raw_20342781'!$F$17</f>
+        <f>'balance_raw_20342781'!$F$20</f>
         <v/>
       </c>
       <c r="C29" s="24">
-        <f>'balance_raw_20342781'!$E$17</f>
+        <f>'balance_raw_20342781'!$E$20</f>
         <v/>
       </c>
       <c r="D29" s="24">
-        <f>'balance_raw_20342781'!$D$17</f>
+        <f>'balance_raw_20342781'!$D$20</f>
         <v/>
       </c>
       <c r="F29" s="25" t="inlineStr">
@@ -6719,15 +7162,15 @@
         </is>
       </c>
       <c r="B30" s="24">
-        <f>'balance_raw_20342781'!$F$54</f>
+        <f>'balance_raw_20342781'!$F$57</f>
         <v/>
       </c>
       <c r="C30" s="24">
-        <f>'balance_raw_20342781'!$E$54</f>
+        <f>'balance_raw_20342781'!$E$57</f>
         <v/>
       </c>
       <c r="D30" s="24">
-        <f>'balance_raw_20342781'!$D$54</f>
+        <f>'balance_raw_20342781'!$D$57</f>
         <v/>
       </c>
       <c r="F30" s="25" t="inlineStr">
@@ -6884,7 +7327,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -7002,7 +7445,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -7178,7 +7621,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -7211,15 +7654,15 @@
         </is>
       </c>
       <c r="B61" s="29">
-        <f>IF('balance_raw_20342781'!$F$28="","—",IF(ABS(B21-'balance_raw_20342781'!$F$28)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw_20342781'!$F$28,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_20342781'!$F$31="","—",IF(ABS(B21-'balance_raw_20342781'!$F$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(B21-'balance_raw_20342781'!$F$31,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C61" s="29">
-        <f>IF('balance_raw_20342781'!$E$28="","—",IF(ABS(C21-'balance_raw_20342781'!$E$28)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw_20342781'!$E$28,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_20342781'!$E$31="","—",IF(ABS(C21-'balance_raw_20342781'!$E$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(C21-'balance_raw_20342781'!$E$31,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D61" s="29">
-        <f>IF('balance_raw_20342781'!$D$28="","—",IF(ABS(D21-'balance_raw_20342781'!$D$28)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw_20342781'!$D$28,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_20342781'!$D$31="","—",IF(ABS(D21-'balance_raw_20342781'!$D$31)&lt;=1,"✓ OK","❌ "&amp;TEXT(D21-'balance_raw_20342781'!$D$31,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F61" s="25" t="inlineStr">
@@ -7235,15 +7678,15 @@
         </is>
       </c>
       <c r="B62" s="29">
-        <f>IF('balance_raw_20342781'!$F$56="","—",IF(ABS(B25-'balance_raw_20342781'!$F$56)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_20342781'!$F$56,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_20342781'!$F$59="","—",IF(ABS(B25-'balance_raw_20342781'!$F$59)&lt;=1,"✓ OK","❌ "&amp;TEXT(B25-'balance_raw_20342781'!$F$59,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="C62" s="29">
-        <f>IF('balance_raw_20342781'!$E$56="","—",IF(ABS(C25-'balance_raw_20342781'!$E$56)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_20342781'!$E$56,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_20342781'!$E$59="","—",IF(ABS(C25-'balance_raw_20342781'!$E$59)&lt;=1,"✓ OK","❌ "&amp;TEXT(C25-'balance_raw_20342781'!$E$59,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="D62" s="29">
-        <f>IF('balance_raw_20342781'!$D$56="","—",IF(ABS(D25-'balance_raw_20342781'!$D$56)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_20342781'!$D$56,"+#,##0;-#,##0")&amp;" t.kr."))</f>
+        <f>IF('balance_raw_20342781'!$D$59="","—",IF(ABS(D25-'balance_raw_20342781'!$D$59)&lt;=1,"✓ OK","❌ "&amp;TEXT(D25-'balance_raw_20342781'!$D$59,"+#,##0;-#,##0")&amp;" t.kr."))</f>
         <v/>
       </c>
       <c r="F62" s="25" t="inlineStr">
@@ -7356,13 +7799,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7401,27 +7844,27 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2020 t.kr.</t>
+          <t>2021 t.kr.</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2021 t.kr.</t>
+          <t>2022 t.kr.</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2022 t.kr.</t>
+          <t>2023 t.kr.</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2023 t.kr.</t>
+          <t>2024 t.kr.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2024 t.kr.</t>
+          <t>2025 t.kr.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
@@ -7438,28 +7881,20 @@
       </c>
       <c r="B3" s="34" t="inlineStr">
         <is>
-          <t>fsa:IncomeFromOtherLongtermInvestmentsAndReceivables</t>
+          <t>fsa:CashFlowsStatement</t>
         </is>
       </c>
       <c r="C3" s="34" t="inlineStr">
         <is>
-          <t>fsa:IncomeFromOtherLongtermInvestmentsAndReceivables</t>
-        </is>
-      </c>
-      <c r="D3" s="35" t="n">
-        <v>2379</v>
-      </c>
-      <c r="E3" s="35" t="n">
-        <v>1408</v>
-      </c>
-      <c r="F3" s="35" t="n">
-        <v>1641</v>
-      </c>
-      <c r="G3" s="35" t="n">
-        <v>3225</v>
-      </c>
+          <t>fsa:CashFlowsStatement</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="n"/>
+      <c r="E3" s="35" t="n"/>
+      <c r="F3" s="35" t="n"/>
+      <c r="G3" s="35" t="n"/>
       <c r="H3" s="35" t="n">
-        <v>4103</v>
+        <v>2</v>
       </c>
       <c r="I3" s="36" t="inlineStr">
         <is>
@@ -7475,29 +7910,27 @@
       </c>
       <c r="B4" s="37" t="inlineStr">
         <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+          <t>fsa:IncomeFromOtherLongtermInvestmentsAndReceivables</t>
         </is>
       </c>
       <c r="C4" s="37" t="inlineStr">
         <is>
-          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+          <t>fsa:IncomeFromOtherLongtermInvestmentsAndReceivables</t>
         </is>
       </c>
       <c r="D4" s="38" t="n">
-        <v>-730</v>
+        <v>1408</v>
       </c>
       <c r="E4" s="38" t="n">
-        <v>1024</v>
+        <v>1641</v>
       </c>
       <c r="F4" s="38" t="n">
-        <v>-343</v>
+        <v>3225</v>
       </c>
       <c r="G4" s="38" t="n">
-        <v>-13269</v>
-      </c>
-      <c r="H4" s="38" t="n">
-        <v>5270</v>
-      </c>
+        <v>4103</v>
+      </c>
+      <c r="H4" s="38" t="n"/>
       <c r="I4" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
@@ -7512,30 +7945,65 @@
       </c>
       <c r="B5" s="34" t="inlineStr">
         <is>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+        </is>
+      </c>
+      <c r="C5" s="34" t="inlineStr">
+        <is>
+          <t>fsa:ReserveForCurrentValueAdjustmentsOfCurrencyGains</t>
+        </is>
+      </c>
+      <c r="D5" s="35" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E5" s="35" t="n">
+        <v>-343</v>
+      </c>
+      <c r="F5" s="35" t="n">
+        <v>-13269</v>
+      </c>
+      <c r="G5" s="35" t="n">
+        <v>5270</v>
+      </c>
+      <c r="H5" s="35" t="n">
+        <v>-9110</v>
+      </c>
+      <c r="I5" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B6" s="37" t="inlineStr">
+        <is>
           <t>fsa:ShorttermPayablesToAssociates</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C6" s="37" t="inlineStr">
         <is>
           <t>fsa:ShorttermPayablesToAssociates</t>
         </is>
       </c>
-      <c r="D5" s="35" t="n">
-        <v>2572</v>
-      </c>
-      <c r="E5" s="35" t="n">
+      <c r="D6" s="38" t="n">
         <v>890</v>
       </c>
-      <c r="F5" s="35" t="n">
+      <c r="E6" s="38" t="n">
         <v>3545</v>
       </c>
-      <c r="G5" s="35" t="n">
+      <c r="F6" s="38" t="n">
         <v>4110</v>
       </c>
-      <c r="H5" s="35" t="n">
+      <c r="G6" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="I5" s="36" t="inlineStr">
+      <c r="H6" s="38" t="n"/>
+      <c r="I6" s="39" t="inlineStr">
         <is>
           <t>Ingen forklaring tilgængelig.</t>
         </is>
